--- a/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>RAVE</t>
   </si>
@@ -656,232 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45284</v>
+      </c>
+      <c r="E7" s="2">
         <v>45193</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45102</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45011</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44920</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44829</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44738</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44647</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44556</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44374</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44283</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44192</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44101</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44010</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43919</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43828</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43737</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43548</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43457</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43366</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43275</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43184</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43093</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43002</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42911</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42820</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42729</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E8" s="3">
         <v>3100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3000</v>
       </c>
       <c r="F8" s="3">
         <v>3000</v>
       </c>
       <c r="G8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H8" s="3">
         <v>2900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2900</v>
-      </c>
-      <c r="U8" s="3">
-        <v>3100</v>
       </c>
       <c r="V8" s="3">
         <v>3100</v>
       </c>
       <c r="W8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="X8" s="3">
         <v>3200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -903,20 +909,20 @@
       <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
+      <c r="M9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
@@ -937,13 +943,13 @@
         <v>100</v>
       </c>
       <c r="U9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>400</v>
       </c>
       <c r="W9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X9" s="3">
         <v>200</v>
@@ -952,28 +958,31 @@
         <v>200</v>
       </c>
       <c r="Z9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA9" s="3">
         <v>300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -995,77 +1004,80 @@
       <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>2600</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>2400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2800</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2700</v>
       </c>
       <c r="V10" s="3">
         <v>2700</v>
       </c>
       <c r="W10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X10" s="3">
         <v>3000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1315,11 +1334,11 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1330,52 +1349,55 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
-      </c>
-      <c r="V14" s="3">
-        <v>200</v>
       </c>
       <c r="W14" s="3">
         <v>200</v>
       </c>
       <c r="X14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3">
         <v>100</v>
       </c>
       <c r="AA14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1395,7 +1417,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1431,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="U15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3">
         <v>100</v>
@@ -1449,7 +1471,7 @@
         <v>100</v>
       </c>
       <c r="AA15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB15" s="3">
         <v>300</v>
@@ -1458,16 +1480,19 @@
         <v>300</v>
       </c>
       <c r="AD15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE15" s="3">
         <v>600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,100 +1522,104 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3300</v>
-      </c>
-      <c r="W17" s="3">
-        <v>2800</v>
       </c>
       <c r="X17" s="3">
         <v>2800</v>
       </c>
       <c r="Y17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Z17" s="3">
         <v>2900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>14300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,91 +1627,94 @@
         <v>500</v>
       </c>
       <c r="E18" s="3">
+        <v>500</v>
+      </c>
+      <c r="F18" s="3">
         <v>800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>500</v>
       </c>
       <c r="G18" s="3">
         <v>500</v>
       </c>
       <c r="H18" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I18" s="3">
         <v>400</v>
       </c>
       <c r="J18" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K18" s="3">
         <v>500</v>
       </c>
       <c r="L18" s="3">
+        <v>500</v>
+      </c>
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>100</v>
       </c>
       <c r="P18" s="3">
         <v>100</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-400</v>
       </c>
       <c r="AA18" s="3">
         <v>-400</v>
       </c>
       <c r="AB18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1747,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1736,11 +1769,11 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1807,8 +1840,11 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,10 +1852,10 @@
         <v>600</v>
       </c>
       <c r="E21" s="3">
+        <v>600</v>
+      </c>
+      <c r="F21" s="3">
         <v>900</v>
-      </c>
-      <c r="F21" s="3">
-        <v>500</v>
       </c>
       <c r="G21" s="3">
         <v>500</v>
@@ -1828,25 +1864,25 @@
         <v>500</v>
       </c>
       <c r="I21" s="3">
+        <v>500</v>
+      </c>
+      <c r="J21" s="3">
         <v>1200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>500</v>
       </c>
       <c r="K21" s="3">
         <v>500</v>
       </c>
       <c r="L21" s="3">
+        <v>500</v>
+      </c>
+      <c r="M21" s="3">
         <v>300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
-      </c>
-      <c r="O21" s="3">
-        <v>100</v>
       </c>
       <c r="P21" s="3">
         <v>100</v>
@@ -1855,52 +1891,55 @@
         <v>100</v>
       </c>
       <c r="R21" s="3">
+        <v>100</v>
+      </c>
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,8 +2030,11 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2000,102 +2042,105 @@
         <v>500</v>
       </c>
       <c r="E23" s="3">
+        <v>500</v>
+      </c>
+      <c r="F23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>500</v>
       </c>
       <c r="K23" s="3">
         <v>500</v>
       </c>
       <c r="L23" s="3">
+        <v>500</v>
+      </c>
+      <c r="M23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>100</v>
       </c>
       <c r="P23" s="3">
         <v>100</v>
       </c>
       <c r="Q23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
@@ -2104,11 +2149,11 @@
         <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-5700</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -2131,32 +2176,32 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>4000</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
@@ -2175,8 +2220,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,19 +2315,22 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
         <v>400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>300</v>
       </c>
       <c r="G26" s="3">
         <v>300</v>
@@ -2288,90 +2339,93 @@
         <v>300</v>
       </c>
       <c r="I26" s="3">
+        <v>300</v>
+      </c>
+      <c r="J26" s="3">
         <v>6800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>500</v>
       </c>
       <c r="K26" s="3">
         <v>500</v>
       </c>
       <c r="L26" s="3">
+        <v>500</v>
+      </c>
+      <c r="M26" s="3">
         <v>300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>100</v>
       </c>
       <c r="P26" s="3">
         <v>100</v>
       </c>
       <c r="Q26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-4500</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>300</v>
       </c>
       <c r="G27" s="3">
         <v>300</v>
@@ -2380,79 +2434,82 @@
         <v>300</v>
       </c>
       <c r="I27" s="3">
+        <v>300</v>
+      </c>
+      <c r="J27" s="3">
         <v>6800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>500</v>
       </c>
       <c r="K27" s="3">
         <v>500</v>
       </c>
       <c r="L27" s="3">
+        <v>500</v>
+      </c>
+      <c r="M27" s="3">
         <v>300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
-      </c>
-      <c r="O27" s="3">
-        <v>100</v>
       </c>
       <c r="P27" s="3">
         <v>100</v>
       </c>
       <c r="Q27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-4500</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2593,14 +2653,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2612,31 +2672,34 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="3">
         <v>-200</v>
       </c>
       <c r="AC29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AD29" s="3">
         <v>-300</v>
       </c>
       <c r="AE29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2885,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2840,11 +2909,11 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2911,19 +2980,22 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>300</v>
       </c>
       <c r="G33" s="3">
         <v>300</v>
@@ -2932,79 +3004,82 @@
         <v>300</v>
       </c>
       <c r="I33" s="3">
+        <v>300</v>
+      </c>
+      <c r="J33" s="3">
         <v>6800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>500</v>
       </c>
       <c r="K33" s="3">
         <v>500</v>
       </c>
       <c r="L33" s="3">
+        <v>500</v>
+      </c>
+      <c r="M33" s="3">
         <v>300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
-      </c>
-      <c r="O33" s="3">
-        <v>100</v>
       </c>
       <c r="P33" s="3">
         <v>100</v>
       </c>
       <c r="Q33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-4500</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,19 +3170,22 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>300</v>
       </c>
       <c r="G35" s="3">
         <v>300</v>
@@ -3116,176 +3194,182 @@
         <v>300</v>
       </c>
       <c r="I35" s="3">
+        <v>300</v>
+      </c>
+      <c r="J35" s="3">
         <v>6800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>500</v>
       </c>
       <c r="K35" s="3">
         <v>500</v>
       </c>
       <c r="L35" s="3">
+        <v>500</v>
+      </c>
+      <c r="M35" s="3">
         <v>300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
-      </c>
-      <c r="O35" s="3">
-        <v>100</v>
       </c>
       <c r="P35" s="3">
         <v>100</v>
       </c>
       <c r="Q35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-4500</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45284</v>
+      </c>
+      <c r="E38" s="2">
         <v>45193</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45102</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45011</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44920</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44829</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44738</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44647</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44556</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44374</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44283</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44192</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44101</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44010</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43919</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43828</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43737</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43548</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43457</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43366</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43275</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43184</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43093</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43002</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42911</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42820</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42729</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
         <v>5900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2300</v>
-      </c>
-      <c r="V41" s="3">
-        <v>1900</v>
       </c>
       <c r="W41" s="3">
         <v>1900</v>
       </c>
       <c r="X41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y41" s="3">
         <v>2000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2200</v>
-      </c>
-      <c r="W43" s="3">
-        <v>2300</v>
       </c>
       <c r="X43" s="3">
         <v>2300</v>
       </c>
       <c r="Y43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Z43" s="3">
         <v>2500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3706,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="3">
         <v>100</v>
@@ -3715,27 +3810,30 @@
         <v>100</v>
       </c>
       <c r="AE44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF44" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
@@ -3750,7 +3848,7 @@
         <v>100</v>
       </c>
       <c r="L45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>200</v>
@@ -3759,167 +3857,173 @@
         <v>200</v>
       </c>
       <c r="O45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="P45" s="3">
         <v>500</v>
       </c>
       <c r="Q45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R45" s="3">
         <v>400</v>
       </c>
       <c r="S45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
       </c>
       <c r="U45" s="3">
+        <v>500</v>
+      </c>
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
-      </c>
-      <c r="X45" s="3">
-        <v>800</v>
       </c>
       <c r="Y45" s="3">
         <v>800</v>
       </c>
       <c r="Z45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E46" s="3">
         <v>7600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8700</v>
-      </c>
-      <c r="P46" s="3">
-        <v>4900</v>
       </c>
       <c r="Q46" s="3">
         <v>4900</v>
       </c>
       <c r="R46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="S46" s="3">
         <v>4000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E47" s="3">
         <v>200</v>
       </c>
       <c r="F47" s="3">
+        <v>200</v>
+      </c>
+      <c r="G47" s="3">
         <v>300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>400</v>
       </c>
       <c r="H47" s="3">
         <v>400</v>
@@ -3928,7 +4032,7 @@
         <v>400</v>
       </c>
       <c r="J47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K47" s="3">
         <v>500</v>
@@ -3937,7 +4041,7 @@
         <v>500</v>
       </c>
       <c r="M47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="N47" s="3">
         <v>300</v>
@@ -3946,150 +4050,156 @@
         <v>300</v>
       </c>
       <c r="P47" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="Q47" s="3">
         <v>700</v>
       </c>
       <c r="R47" s="3">
+        <v>700</v>
+      </c>
+      <c r="S47" s="3">
         <v>400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1000</v>
-      </c>
-      <c r="V47" s="3">
-        <v>1200</v>
       </c>
       <c r="W47" s="3">
         <v>1200</v>
       </c>
       <c r="X47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>300</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4109,7 +4219,7 @@
         <v>300</v>
       </c>
       <c r="I49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J49" s="3">
         <v>200</v>
@@ -4124,7 +4234,7 @@
         <v>200</v>
       </c>
       <c r="N49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O49" s="3">
         <v>100</v>
@@ -4133,7 +4243,7 @@
         <v>100</v>
       </c>
       <c r="Q49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R49" s="3">
         <v>200</v>
@@ -4168,8 +4278,8 @@
       <c r="AB49" s="3">
         <v>200</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
+      <c r="AC49" s="3">
+        <v>200</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,31 +4480,34 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E52" s="3">
         <v>5200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>5800</v>
       </c>
       <c r="I52" s="3">
         <v>5800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
+      <c r="J52" s="3">
+        <v>5800</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
@@ -4396,8 +4515,8 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -4412,31 +4531,31 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>4200</v>
       </c>
       <c r="T52" s="3">
         <v>4200</v>
       </c>
       <c r="U52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V52" s="3">
         <v>4300</v>
-      </c>
-      <c r="V52" s="3">
-        <v>3600</v>
       </c>
       <c r="W52" s="3">
         <v>3600</v>
       </c>
       <c r="X52" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="Y52" s="3">
         <v>3700</v>
       </c>
       <c r="Z52" s="3">
-        <v>200</v>
+        <v>3700</v>
       </c>
       <c r="AA52" s="3">
         <v>200</v>
@@ -4445,19 +4564,22 @@
         <v>200</v>
       </c>
       <c r="AC52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AD52" s="3">
         <v>500</v>
       </c>
       <c r="AE52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF52" s="3">
         <v>200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E54" s="3">
         <v>14700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11100</v>
-      </c>
-      <c r="W54" s="3">
-        <v>11500</v>
       </c>
       <c r="X54" s="3">
         <v>11500</v>
       </c>
       <c r="Y54" s="3">
+        <v>11500</v>
+      </c>
+      <c r="Z54" s="3">
         <v>11000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,70 +4837,71 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>500</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
       </c>
       <c r="G57" s="3">
+        <v>500</v>
+      </c>
+      <c r="H57" s="3">
         <v>600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>700</v>
       </c>
       <c r="I57" s="3">
         <v>700</v>
       </c>
       <c r="J57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
       <c r="L57" s="3">
+        <v>600</v>
+      </c>
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
-      </c>
-      <c r="P57" s="3">
-        <v>900</v>
       </c>
       <c r="Q57" s="3">
         <v>900</v>
       </c>
       <c r="R57" s="3">
+        <v>900</v>
+      </c>
+      <c r="S57" s="3">
         <v>700</v>
-      </c>
-      <c r="S57" s="3">
-        <v>900</v>
       </c>
       <c r="T57" s="3">
         <v>900</v>
       </c>
       <c r="U57" s="3">
+        <v>900</v>
+      </c>
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
-      </c>
-      <c r="W57" s="3">
-        <v>800</v>
       </c>
       <c r="X57" s="3">
         <v>800</v>
@@ -4780,36 +4910,39 @@
         <v>800</v>
       </c>
       <c r="Z57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA57" s="3">
         <v>700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4824,19 +4957,19 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1700</v>
       </c>
       <c r="L58" s="3">
         <v>1700</v>
       </c>
       <c r="M58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N58" s="3">
         <v>1800</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -4850,8 +4983,8 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -4878,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>1000</v>
@@ -4889,195 +5022,204 @@
       <c r="AE58" s="3">
         <v>1000</v>
       </c>
-      <c r="AF58" s="3" t="s">
+      <c r="AF58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1600</v>
       </c>
       <c r="P59" s="3">
         <v>1600</v>
       </c>
       <c r="Q59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1000</v>
       </c>
       <c r="AA59" s="3">
         <v>1000</v>
       </c>
       <c r="AB59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC59" s="3">
         <v>1400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1900</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>1400</v>
       </c>
       <c r="AF59" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>2500</v>
       </c>
       <c r="Q60" s="3">
         <v>2500</v>
       </c>
       <c r="R60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5112,7 +5254,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>2200</v>
@@ -5124,7 +5266,7 @@
         <v>2200</v>
       </c>
       <c r="R61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="S61" s="3">
         <v>1500</v>
@@ -5133,7 +5275,7 @@
         <v>1500</v>
       </c>
       <c r="U61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="V61" s="3">
         <v>1600</v>
@@ -5151,117 +5293,123 @@
         <v>1600</v>
       </c>
       <c r="AA61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB61" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>2700</v>
       </c>
       <c r="AC61" s="3">
         <v>2700</v>
       </c>
       <c r="AD61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE61" s="3">
         <v>2800</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,16 +5690,19 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3900</v>
-      </c>
-      <c r="E66" s="3">
-        <v>3800</v>
       </c>
       <c r="F66" s="3">
         <v>3800</v>
@@ -5554,82 +5711,85 @@
         <v>3800</v>
       </c>
       <c r="H66" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="I66" s="3">
         <v>5100</v>
       </c>
       <c r="J66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K66" s="3">
         <v>4700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E72" s="3">
         <v>2800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-8700</v>
       </c>
       <c r="R72" s="3">
         <v>-8700</v>
       </c>
       <c r="S72" s="3">
-        <v>-4200</v>
+        <v>-8700</v>
       </c>
       <c r="T72" s="3">
         <v>-4200</v>
       </c>
       <c r="U72" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="V72" s="3">
         <v>-4500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E76" s="3">
         <v>10900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>100</v>
-      </c>
-      <c r="S76" s="3">
-        <v>4700</v>
       </c>
       <c r="T76" s="3">
         <v>4700</v>
       </c>
       <c r="U76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="V76" s="3">
         <v>4400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,116 +6770,122 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45284</v>
+      </c>
+      <c r="E80" s="2">
         <v>45193</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45102</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45011</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44920</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44829</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44738</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44647</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44556</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44374</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44283</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44192</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44101</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44010</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43919</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43828</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43737</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43548</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43457</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43366</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43275</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43184</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43093</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43002</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42911</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42820</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42729</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>300</v>
       </c>
       <c r="G81" s="3">
         <v>300</v>
@@ -6700,79 +6894,82 @@
         <v>300</v>
       </c>
       <c r="I81" s="3">
+        <v>300</v>
+      </c>
+      <c r="J81" s="3">
         <v>6800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>500</v>
       </c>
       <c r="K81" s="3">
         <v>500</v>
       </c>
       <c r="L81" s="3">
+        <v>500</v>
+      </c>
+      <c r="M81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
-      </c>
-      <c r="O81" s="3">
-        <v>100</v>
       </c>
       <c r="P81" s="3">
         <v>100</v>
       </c>
       <c r="Q81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-4500</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6826,7 +7024,7 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -6862,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -6880,7 +7078,7 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>300</v>
@@ -6889,16 +7087,19 @@
         <v>300</v>
       </c>
       <c r="AD83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE83" s="3">
         <v>600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>400</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-500</v>
       </c>
       <c r="S89" s="3">
         <v>-500</v>
       </c>
       <c r="T89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U89" s="3">
         <v>100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7492,13 +7712,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -7507,7 +7727,7 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7516,11 +7736,11 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -7552,31 +7772,34 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-300</v>
       </c>
       <c r="AD91" s="3">
         <v>-300</v>
       </c>
       <c r="AE91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7768,35 +7997,35 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -7822,37 +8051,40 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>600</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,13 +8495,16 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -8268,41 +8513,41 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1600</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>3600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -8310,11 +8555,11 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -8325,28 +8570,31 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>2900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>3400</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>RAVE</t>
   </si>
@@ -656,238 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45375</v>
+      </c>
+      <c r="E7" s="2">
         <v>45284</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45193</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45102</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45011</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44920</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44829</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44738</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44647</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44556</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44374</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44283</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44192</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44101</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44010</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43919</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43828</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43737</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43548</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43457</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43366</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43275</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43184</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43093</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43002</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42911</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42820</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42729</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3000</v>
       </c>
       <c r="G8" s="3">
         <v>3000</v>
       </c>
       <c r="H8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2900</v>
-      </c>
-      <c r="V8" s="3">
-        <v>3100</v>
       </c>
       <c r="W8" s="3">
         <v>3100</v>
       </c>
       <c r="X8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>3200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -912,20 +919,20 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
+      <c r="N9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>100</v>
@@ -946,13 +953,13 @@
         <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
         <v>400</v>
       </c>
       <c r="X9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Y9" s="3">
         <v>200</v>
@@ -961,28 +968,31 @@
         <v>200</v>
       </c>
       <c r="AA9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB9" s="3">
         <v>300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1007,77 +1017,80 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>2600</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>2400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2800</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2700</v>
       </c>
       <c r="W10" s="3">
         <v>2700</v>
       </c>
       <c r="X10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Y10" s="3">
         <v>3000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1337,11 +1357,11 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1352,52 +1372,55 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
-      </c>
-      <c r="W14" s="3">
-        <v>200</v>
       </c>
       <c r="X14" s="3">
         <v>200</v>
       </c>
       <c r="Y14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>100</v>
       </c>
       <c r="AB14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="3">
         <v>500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1420,7 +1443,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1456,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W15" s="3">
         <v>100</v>
@@ -1474,7 +1497,7 @@
         <v>100</v>
       </c>
       <c r="AB15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AC15" s="3">
         <v>300</v>
@@ -1483,16 +1506,19 @@
         <v>300</v>
       </c>
       <c r="AE15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF15" s="3">
         <v>600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3300</v>
-      </c>
-      <c r="X17" s="3">
-        <v>2800</v>
       </c>
       <c r="Y17" s="3">
         <v>2800</v>
       </c>
       <c r="Z17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AA17" s="3">
         <v>2900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>14300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E18" s="3">
         <v>500</v>
       </c>
       <c r="F18" s="3">
+        <v>500</v>
+      </c>
+      <c r="G18" s="3">
         <v>800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>500</v>
       </c>
       <c r="H18" s="3">
         <v>500</v>
       </c>
       <c r="I18" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J18" s="3">
         <v>400</v>
       </c>
       <c r="K18" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L18" s="3">
         <v>500</v>
       </c>
       <c r="M18" s="3">
+        <v>500</v>
+      </c>
+      <c r="N18" s="3">
         <v>300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
-      </c>
-      <c r="P18" s="3">
-        <v>100</v>
       </c>
       <c r="Q18" s="3">
         <v>100</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-400</v>
       </c>
       <c r="AB18" s="3">
         <v>-400</v>
       </c>
       <c r="AC18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1772,11 +1806,11 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1843,22 +1877,25 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E21" s="3">
         <v>600</v>
       </c>
       <c r="F21" s="3">
+        <v>600</v>
+      </c>
+      <c r="G21" s="3">
         <v>900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>500</v>
       </c>
       <c r="H21" s="3">
         <v>500</v>
@@ -1867,25 +1904,25 @@
         <v>500</v>
       </c>
       <c r="J21" s="3">
+        <v>500</v>
+      </c>
+      <c r="K21" s="3">
         <v>1200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>500</v>
       </c>
       <c r="L21" s="3">
         <v>500</v>
       </c>
       <c r="M21" s="3">
+        <v>500</v>
+      </c>
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>500</v>
-      </c>
-      <c r="P21" s="3">
-        <v>100</v>
       </c>
       <c r="Q21" s="3">
         <v>100</v>
@@ -1894,52 +1931,55 @@
         <v>100</v>
       </c>
       <c r="S21" s="3">
+        <v>100</v>
+      </c>
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,117 +2073,123 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E23" s="3">
         <v>500</v>
       </c>
       <c r="F23" s="3">
+        <v>500</v>
+      </c>
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>500</v>
       </c>
       <c r="L23" s="3">
         <v>500</v>
       </c>
       <c r="M23" s="3">
+        <v>500</v>
+      </c>
+      <c r="N23" s="3">
         <v>300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>100</v>
       </c>
       <c r="Q23" s="3">
         <v>100</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>200</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
       <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
@@ -2152,11 +2198,11 @@
         <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-5700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -2179,32 +2225,32 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>4000</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,22 +2367,25 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>300</v>
       </c>
       <c r="H26" s="3">
         <v>300</v>
@@ -2342,93 +2394,96 @@
         <v>300</v>
       </c>
       <c r="J26" s="3">
+        <v>300</v>
+      </c>
+      <c r="K26" s="3">
         <v>6800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>500</v>
       </c>
       <c r="L26" s="3">
         <v>500</v>
       </c>
       <c r="M26" s="3">
+        <v>500</v>
+      </c>
+      <c r="N26" s="3">
         <v>300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>100</v>
       </c>
       <c r="Q26" s="3">
         <v>100</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-4500</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>300</v>
       </c>
       <c r="H27" s="3">
         <v>300</v>
@@ -2437,79 +2492,82 @@
         <v>300</v>
       </c>
       <c r="J27" s="3">
+        <v>300</v>
+      </c>
+      <c r="K27" s="3">
         <v>6800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>500</v>
       </c>
       <c r="L27" s="3">
         <v>500</v>
       </c>
       <c r="M27" s="3">
+        <v>500</v>
+      </c>
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>100</v>
       </c>
       <c r="Q27" s="3">
         <v>100</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-4500</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2656,14 +2717,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2675,31 +2736,34 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="3">
         <v>-200</v>
       </c>
       <c r="AD29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AE29" s="3">
         <v>-300</v>
       </c>
       <c r="AF29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2912,11 +2982,11 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2983,22 +3053,25 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>300</v>
       </c>
       <c r="H33" s="3">
         <v>300</v>
@@ -3007,79 +3080,82 @@
         <v>300</v>
       </c>
       <c r="J33" s="3">
+        <v>300</v>
+      </c>
+      <c r="K33" s="3">
         <v>6800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>500</v>
       </c>
       <c r="L33" s="3">
         <v>500</v>
       </c>
       <c r="M33" s="3">
+        <v>500</v>
+      </c>
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>100</v>
       </c>
       <c r="Q33" s="3">
         <v>100</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-4500</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,22 +3249,25 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>300</v>
       </c>
       <c r="H35" s="3">
         <v>300</v>
@@ -3197,179 +3276,185 @@
         <v>300</v>
       </c>
       <c r="J35" s="3">
+        <v>300</v>
+      </c>
+      <c r="K35" s="3">
         <v>6800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>500</v>
       </c>
       <c r="L35" s="3">
         <v>500</v>
       </c>
       <c r="M35" s="3">
+        <v>500</v>
+      </c>
+      <c r="N35" s="3">
         <v>300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>100</v>
       </c>
       <c r="Q35" s="3">
         <v>100</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-4500</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45375</v>
+      </c>
+      <c r="E38" s="2">
         <v>45284</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45193</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45102</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45011</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44920</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44829</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44738</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44647</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44556</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44374</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44283</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44192</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44101</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44010</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43919</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43828</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43737</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43548</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43457</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43366</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43275</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43184</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43093</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43002</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42911</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42820</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42729</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E41" s="3">
         <v>5300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2300</v>
-      </c>
-      <c r="W41" s="3">
-        <v>1900</v>
       </c>
       <c r="X41" s="3">
         <v>1900</v>
       </c>
       <c r="Y41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,103 +3718,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2200</v>
-      </c>
-      <c r="X43" s="3">
-        <v>2300</v>
       </c>
       <c r="Y43" s="3">
         <v>2300</v>
       </c>
       <c r="Z43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA43" s="3">
         <v>2500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3804,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="AC44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="3">
         <v>100</v>
@@ -3813,13 +3909,16 @@
         <v>100</v>
       </c>
       <c r="AF44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG44" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3827,16 +3926,16 @@
         <v>500</v>
       </c>
       <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I45" s="3">
         <v>100</v>
@@ -3851,7 +3950,7 @@
         <v>100</v>
       </c>
       <c r="M45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
@@ -3860,156 +3959,162 @@
         <v>200</v>
       </c>
       <c r="P45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>500</v>
       </c>
       <c r="R45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S45" s="3">
         <v>400</v>
       </c>
       <c r="T45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U45" s="3">
         <v>500</v>
       </c>
       <c r="V45" s="3">
+        <v>500</v>
+      </c>
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>800</v>
       </c>
       <c r="Z45" s="3">
         <v>800</v>
       </c>
       <c r="AA45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8700</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>4900</v>
       </c>
       <c r="R46" s="3">
         <v>4900</v>
       </c>
       <c r="S46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="T46" s="3">
         <v>4000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4017,16 +4122,16 @@
         <v>300</v>
       </c>
       <c r="E47" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F47" s="3">
         <v>200</v>
       </c>
       <c r="G47" s="3">
+        <v>200</v>
+      </c>
+      <c r="H47" s="3">
         <v>300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>400</v>
       </c>
       <c r="I47" s="3">
         <v>400</v>
@@ -4035,7 +4140,7 @@
         <v>400</v>
       </c>
       <c r="K47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L47" s="3">
         <v>500</v>
@@ -4044,7 +4149,7 @@
         <v>500</v>
       </c>
       <c r="N47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
@@ -4053,153 +4158,159 @@
         <v>300</v>
       </c>
       <c r="Q47" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="R47" s="3">
         <v>700</v>
       </c>
       <c r="S47" s="3">
+        <v>700</v>
+      </c>
+      <c r="T47" s="3">
         <v>400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1000</v>
-      </c>
-      <c r="W47" s="3">
-        <v>1200</v>
       </c>
       <c r="X47" s="3">
         <v>1200</v>
       </c>
       <c r="Y47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z47" s="3">
         <v>1000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>300</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
       <c r="AC47" s="3">
         <v>0</v>
       </c>
       <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
         <v>100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4222,7 +4333,7 @@
         <v>300</v>
       </c>
       <c r="J49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K49" s="3">
         <v>200</v>
@@ -4237,7 +4348,7 @@
         <v>200</v>
       </c>
       <c r="O49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P49" s="3">
         <v>100</v>
@@ -4246,7 +4357,7 @@
         <v>100</v>
       </c>
       <c r="R49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S49" s="3">
         <v>200</v>
@@ -4281,8 +4392,8 @@
       <c r="AC49" s="3">
         <v>200</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
+      <c r="AD49" s="3">
+        <v>200</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,34 +4600,37 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E52" s="3">
         <v>5300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>5800</v>
       </c>
       <c r="J52" s="3">
         <v>5800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
+      <c r="K52" s="3">
+        <v>5800</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>8</v>
@@ -4518,8 +4638,8 @@
       <c r="M52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -4534,31 +4654,31 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>200</v>
-      </c>
-      <c r="T52" s="3">
-        <v>4200</v>
       </c>
       <c r="U52" s="3">
         <v>4200</v>
       </c>
       <c r="V52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="W52" s="3">
         <v>4300</v>
-      </c>
-      <c r="W52" s="3">
-        <v>3600</v>
       </c>
       <c r="X52" s="3">
         <v>3600</v>
       </c>
       <c r="Y52" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="Z52" s="3">
         <v>3700</v>
       </c>
       <c r="AA52" s="3">
-        <v>200</v>
+        <v>3700</v>
       </c>
       <c r="AB52" s="3">
         <v>200</v>
@@ -4567,19 +4687,22 @@
         <v>200</v>
       </c>
       <c r="AD52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AE52" s="3">
         <v>500</v>
       </c>
       <c r="AF52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG52" s="3">
         <v>200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E54" s="3">
         <v>14200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11100</v>
-      </c>
-      <c r="X54" s="3">
-        <v>11500</v>
       </c>
       <c r="Y54" s="3">
         <v>11500</v>
       </c>
       <c r="Z54" s="3">
+        <v>11500</v>
+      </c>
+      <c r="AA54" s="3">
         <v>11000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4847,64 +4978,64 @@
         <v>700</v>
       </c>
       <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
         <v>600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>700</v>
       </c>
       <c r="J57" s="3">
         <v>700</v>
       </c>
       <c r="K57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L57" s="3">
         <v>600</v>
       </c>
       <c r="M57" s="3">
+        <v>600</v>
+      </c>
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>900</v>
       </c>
       <c r="R57" s="3">
         <v>900</v>
       </c>
       <c r="S57" s="3">
+        <v>900</v>
+      </c>
+      <c r="T57" s="3">
         <v>700</v>
-      </c>
-      <c r="T57" s="3">
-        <v>900</v>
       </c>
       <c r="U57" s="3">
         <v>900</v>
       </c>
       <c r="V57" s="3">
+        <v>900</v>
+      </c>
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1000</v>
-      </c>
-      <c r="X57" s="3">
-        <v>800</v>
       </c>
       <c r="Y57" s="3">
         <v>800</v>
@@ -4913,28 +5044,31 @@
         <v>800</v>
       </c>
       <c r="AA57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB57" s="3">
         <v>700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4944,8 +5078,8 @@
       <c r="E58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -4960,19 +5094,19 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1700</v>
       </c>
       <c r="M58" s="3">
         <v>1700</v>
       </c>
       <c r="N58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O58" s="3">
         <v>1800</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -4986,8 +5120,8 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5014,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>1000</v>
@@ -5025,201 +5159,210 @@
       <c r="AF58" s="3">
         <v>1000</v>
       </c>
-      <c r="AG58" s="3" t="s">
+      <c r="AG58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1700</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1600</v>
       </c>
       <c r="Q59" s="3">
         <v>1600</v>
       </c>
       <c r="R59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>1000</v>
       </c>
       <c r="AB59" s="3">
         <v>1000</v>
       </c>
       <c r="AC59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD59" s="3">
         <v>1400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1900</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>1400</v>
       </c>
       <c r="AG59" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>2500</v>
       </c>
       <c r="R60" s="3">
         <v>2500</v>
       </c>
       <c r="S60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="T60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5257,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>2200</v>
@@ -5269,7 +5412,7 @@
         <v>2200</v>
       </c>
       <c r="S61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="T61" s="3">
         <v>1500</v>
@@ -5278,7 +5421,7 @@
         <v>1500</v>
       </c>
       <c r="V61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="W61" s="3">
         <v>1600</v>
@@ -5296,120 +5439,126 @@
         <v>1600</v>
       </c>
       <c r="AB61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC61" s="3">
         <v>1500</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>2700</v>
       </c>
       <c r="AD61" s="3">
         <v>2700</v>
       </c>
       <c r="AE61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AF61" s="3">
         <v>2800</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,19 +5848,22 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3900</v>
-      </c>
-      <c r="F66" s="3">
-        <v>3800</v>
       </c>
       <c r="G66" s="3">
         <v>3800</v>
@@ -5714,82 +5872,85 @@
         <v>3800</v>
       </c>
       <c r="I66" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="J66" s="3">
         <v>5100</v>
       </c>
       <c r="K66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L66" s="3">
         <v>4700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-8700</v>
       </c>
       <c r="S72" s="3">
         <v>-8700</v>
       </c>
       <c r="T72" s="3">
-        <v>-4200</v>
+        <v>-8700</v>
       </c>
       <c r="U72" s="3">
         <v>-4200</v>
       </c>
       <c r="V72" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="W72" s="3">
         <v>-4500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E76" s="3">
         <v>11100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>100</v>
-      </c>
-      <c r="T76" s="3">
-        <v>4700</v>
       </c>
       <c r="U76" s="3">
         <v>4700</v>
       </c>
       <c r="V76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="W76" s="3">
         <v>4400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,122 +6962,128 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45375</v>
+      </c>
+      <c r="E80" s="2">
         <v>45284</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45193</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45102</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45011</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44920</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44829</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44738</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44647</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44556</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44374</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44283</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44192</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44101</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44010</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43919</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43828</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43737</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43548</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43457</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43366</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43275</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43184</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43093</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43002</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42911</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42820</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42729</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>300</v>
       </c>
       <c r="H81" s="3">
         <v>300</v>
@@ -6897,79 +7092,82 @@
         <v>300</v>
       </c>
       <c r="J81" s="3">
+        <v>300</v>
+      </c>
+      <c r="K81" s="3">
         <v>6800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>500</v>
       </c>
       <c r="L81" s="3">
         <v>500</v>
       </c>
       <c r="M81" s="3">
+        <v>500</v>
+      </c>
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>100</v>
       </c>
       <c r="Q81" s="3">
         <v>100</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-4500</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7027,7 +7226,7 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7063,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -7081,7 +7280,7 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>300</v>
@@ -7090,16 +7289,19 @@
         <v>300</v>
       </c>
       <c r="AE83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF83" s="3">
         <v>600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>400</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-500</v>
       </c>
       <c r="T89" s="3">
         <v>-500</v>
       </c>
       <c r="U89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V89" s="3">
         <v>100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7715,13 +7936,13 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -7730,7 +7951,7 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -7739,11 +7960,11 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -7775,31 +7996,34 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-300</v>
       </c>
       <c r="AE91" s="3">
         <v>-300</v>
       </c>
       <c r="AF91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8000,35 +8230,35 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -8054,37 +8284,40 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>600</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,17 +8741,20 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -8516,41 +8762,41 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-3600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>3600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -8558,11 +8804,11 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -8573,28 +8819,31 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4900</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>2900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>RAVE</t>
   </si>
@@ -656,289 +656,303 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45375</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45284</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45193</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45102</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45011</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44920</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44829</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44738</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44647</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44556</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44374</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44283</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44192</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44101</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44010</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43919</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43828</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43737</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43548</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43457</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43366</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43275</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43184</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43093</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43002</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42911</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42820</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42729</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F8" s="3">
         <v>3000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2900</v>
       </c>
       <c r="J8" s="3">
         <v>3000</v>
       </c>
       <c r="K8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M8" s="3">
         <v>2800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2700</v>
       </c>
       <c r="N8" s="3">
         <v>2600</v>
       </c>
       <c r="O8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>4200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>5400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>5300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>6500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>6800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>800</v>
+      </c>
+      <c r="F9" s="3">
+        <v>800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1000</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
+      <c r="L9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3">
-        <v>100</v>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
         <v>100</v>
@@ -956,141 +970,153 @@
         <v>100</v>
       </c>
       <c r="W9" s="3">
+        <v>100</v>
+      </c>
+      <c r="X9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="3">
         <v>400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>400</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>200</v>
       </c>
       <c r="AA9" s="3">
         <v>200</v>
       </c>
       <c r="AB9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD9" s="3">
         <v>300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>3800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>3900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>2600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2600</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2800</v>
       </c>
       <c r="W10" s="3">
         <v>2700</v>
       </c>
       <c r="X10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y10" s="3">
         <v>2700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AA10" s="3">
         <v>3000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>3400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1151,10 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1251,14 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,31 +1355,37 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1360,14 +1400,14 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1375,60 +1415,66 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
-        <v>100</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>100</v>
-      </c>
       <c r="AB14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>-100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>5100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1446,10 +1492,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1482,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="W15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
         <v>100</v>
@@ -1500,25 +1546,31 @@
         <v>100</v>
       </c>
       <c r="AC15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AD15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AE15" s="3">
         <v>300</v>
       </c>
       <c r="AF15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH15" s="3">
         <v>600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1602,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="E17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2600</v>
       </c>
       <c r="K17" s="3">
         <v>2400</v>
       </c>
       <c r="L17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N17" s="3">
         <v>2100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>2000</v>
       </c>
       <c r="R17" s="3">
         <v>1800</v>
       </c>
       <c r="S17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>5600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>8200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>14300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="E18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>800</v>
+      </c>
+      <c r="G18" s="3">
         <v>500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>800</v>
       </c>
       <c r="H18" s="3">
         <v>500</v>
       </c>
       <c r="I18" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="J18" s="3">
         <v>400</v>
       </c>
       <c r="K18" s="3">
+        <v>500</v>
+      </c>
+      <c r="L18" s="3">
         <v>400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
+        <v>400</v>
+      </c>
+      <c r="N18" s="3">
         <v>500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
       </c>
-      <c r="Q18" s="3">
-        <v>100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>100</v>
-      </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18" s="3">
+        <v>100</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,41 +1848,43 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1880,129 +1948,141 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>500</v>
       </c>
       <c r="J21" s="3">
         <v>500</v>
       </c>
       <c r="K21" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="L21" s="3">
         <v>500</v>
       </c>
       <c r="M21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
+        <v>500</v>
+      </c>
+      <c r="P21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>500</v>
       </c>
-      <c r="Q21" s="3">
-        <v>100</v>
-      </c>
-      <c r="R21" s="3">
-        <v>100</v>
-      </c>
       <c r="S21" s="3">
         <v>100</v>
       </c>
       <c r="T21" s="3">
+        <v>100</v>
+      </c>
+      <c r="U21" s="3">
+        <v>100</v>
+      </c>
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
-        <v>100</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
+        <v>100</v>
+      </c>
+      <c r="X21" s="3">
         <v>400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>300</v>
       </c>
-      <c r="AA21" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2076,106 +2156,118 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>500</v>
       </c>
       <c r="J23" s="3">
         <v>400</v>
       </c>
       <c r="K23" s="3">
+        <v>500</v>
+      </c>
+      <c r="L23" s="3">
+        <v>400</v>
+      </c>
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>100</v>
-      </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23" s="3">
+        <v>100</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2183,32 +2275,32 @@
         <v>200</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
-      </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>-5700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -2228,35 +2320,35 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
-      </c>
       <c r="Z24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
@@ -2272,8 +2364,14 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2468,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>900</v>
+      </c>
+      <c r="F26" s="3">
         <v>700</v>
-      </c>
-      <c r="E26" s="3">
-        <v>600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>400</v>
       </c>
       <c r="G26" s="3">
         <v>600</v>
       </c>
       <c r="H26" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I26" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J26" s="3">
         <v>300</v>
       </c>
       <c r="K26" s="3">
+        <v>300</v>
+      </c>
+      <c r="L26" s="3">
+        <v>300</v>
+      </c>
+      <c r="M26" s="3">
         <v>6800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
-      <c r="R26" s="3">
-        <v>100</v>
-      </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26" s="3">
+        <v>100</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-4500</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
-      <c r="Z26" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>900</v>
+      </c>
+      <c r="F27" s="3">
         <v>700</v>
-      </c>
-      <c r="E27" s="3">
-        <v>600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>400</v>
       </c>
       <c r="G27" s="3">
         <v>600</v>
       </c>
       <c r="H27" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I27" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J27" s="3">
         <v>300</v>
       </c>
       <c r="K27" s="3">
+        <v>300</v>
+      </c>
+      <c r="L27" s="3">
+        <v>300</v>
+      </c>
+      <c r="M27" s="3">
         <v>6800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>100</v>
-      </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27" s="3">
+        <v>100</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-4500</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>200</v>
       </c>
-      <c r="Z27" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2780,14 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2720,17 +2842,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2739,31 +2861,37 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>-300</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>-400</v>
       </c>
       <c r="AH29" s="3">
         <v>-300</v>
       </c>
+      <c r="AI29" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2988,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,41 +3092,47 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3056,106 +3196,118 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>900</v>
+      </c>
+      <c r="F33" s="3">
         <v>700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>400</v>
       </c>
       <c r="G33" s="3">
         <v>600</v>
       </c>
       <c r="H33" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I33" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J33" s="3">
         <v>300</v>
       </c>
       <c r="K33" s="3">
+        <v>300</v>
+      </c>
+      <c r="L33" s="3">
+        <v>300</v>
+      </c>
+      <c r="M33" s="3">
         <v>6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>100</v>
-      </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33" s="3">
+        <v>100</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-4500</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>3300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3404,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>900</v>
+      </c>
+      <c r="F35" s="3">
         <v>700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>400</v>
       </c>
       <c r="G35" s="3">
         <v>600</v>
       </c>
       <c r="H35" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I35" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J35" s="3">
         <v>300</v>
       </c>
       <c r="K35" s="3">
+        <v>300</v>
+      </c>
+      <c r="L35" s="3">
+        <v>300</v>
+      </c>
+      <c r="M35" s="3">
         <v>6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>100</v>
-      </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T35" s="3">
+        <v>100</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-4500</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>3300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45375</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45284</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45193</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45102</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45011</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44920</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44829</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44738</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44647</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44556</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44374</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44283</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44192</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44101</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44010</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43919</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43828</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43737</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43548</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43457</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43366</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43275</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43184</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43093</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43002</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42911</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42820</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42729</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3659,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,114 +3697,122 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F41" s="3">
         <v>6300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>5900</v>
       </c>
       <c r="G41" s="3">
         <v>5300</v>
       </c>
       <c r="H41" s="3">
+        <v>5900</v>
+      </c>
+      <c r="I41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J41" s="3">
         <v>3900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>6300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>1000</v>
       </c>
       <c r="AC41" s="3">
         <v>1400</v>
       </c>
       <c r="AD41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3721,8 +3901,14 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3730,120 +3916,126 @@
         <v>1400</v>
       </c>
       <c r="E43" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F43" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="G43" s="3">
         <v>1300</v>
       </c>
       <c r="H43" s="3">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="I43" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="J43" s="3">
         <v>1700</v>
       </c>
       <c r="K43" s="3">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="L43" s="3">
         <v>1700</v>
       </c>
       <c r="M43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O43" s="3">
         <v>1600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1500</v>
-      </c>
-      <c r="S43" s="3">
-        <v>1600</v>
-      </c>
-      <c r="T43" s="3">
-        <v>2100</v>
       </c>
       <c r="U43" s="3">
         <v>1600</v>
       </c>
       <c r="V43" s="3">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="W43" s="3">
         <v>1600</v>
       </c>
       <c r="X43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Z43" s="3">
         <v>2200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2400</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>3500</v>
       </c>
       <c r="AE43" s="3">
         <v>3600</v>
       </c>
       <c r="AF43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AH43" s="3">
         <v>2900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>2700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3903,39 +4095,45 @@
         <v>0</v>
       </c>
       <c r="AD44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF44" s="3">
         <v>100</v>
       </c>
       <c r="AG44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI44" s="3">
         <v>200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>100</v>
@@ -3953,369 +4151,393 @@
         <v>100</v>
       </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
       <c r="Q45" s="3">
+        <v>200</v>
+      </c>
+      <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
-      </c>
-      <c r="X45" s="3">
-        <v>800</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>900</v>
       </c>
       <c r="Z45" s="3">
         <v>800</v>
       </c>
       <c r="AA45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F46" s="3">
         <v>8200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>9500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>8700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>5200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>6100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>8300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>5100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>6900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>4600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>300</v>
-      </c>
-      <c r="F47" s="3">
-        <v>200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>400</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>400</v>
       </c>
       <c r="L47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N47" s="3">
         <v>500</v>
       </c>
       <c r="O47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="P47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="Q47" s="3">
         <v>300</v>
       </c>
       <c r="R47" s="3">
+        <v>300</v>
+      </c>
+      <c r="S47" s="3">
+        <v>300</v>
+      </c>
+      <c r="T47" s="3">
         <v>700</v>
-      </c>
-      <c r="S47" s="3">
-        <v>700</v>
-      </c>
-      <c r="T47" s="3">
-        <v>400</v>
       </c>
       <c r="U47" s="3">
         <v>700</v>
       </c>
       <c r="V47" s="3">
+        <v>400</v>
+      </c>
+      <c r="W47" s="3">
+        <v>700</v>
+      </c>
+      <c r="X47" s="3">
         <v>500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>300</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>0</v>
-      </c>
       <c r="AE47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH47" s="3">
         <v>200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>4100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>3800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>4400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>5800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3">
         <v>300</v>
@@ -4336,10 +4558,10 @@
         <v>300</v>
       </c>
       <c r="K49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M49" s="3">
         <v>200</v>
@@ -4351,19 +4573,19 @@
         <v>200</v>
       </c>
       <c r="P49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R49" s="3">
         <v>100</v>
       </c>
       <c r="S49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U49" s="3">
         <v>200</v>
@@ -4395,11 +4617,11 @@
       <c r="AD49" s="3">
         <v>200</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
+      <c r="AE49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>200</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
@@ -4407,8 +4629,14 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4733,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,49 +4837,55 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>5100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>5300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>5600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>5800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -4657,52 +4897,58 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>4200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>4200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>3600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3700</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>200</v>
       </c>
       <c r="AD52" s="3">
         <v>200</v>
       </c>
       <c r="AE52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG52" s="3">
         <v>500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +5045,118 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F54" s="3">
         <v>15000</v>
-      </c>
-      <c r="E54" s="3">
-        <v>14200</v>
-      </c>
-      <c r="F54" s="3">
-        <v>14700</v>
       </c>
       <c r="G54" s="3">
         <v>14200</v>
       </c>
       <c r="H54" s="3">
+        <v>14700</v>
+      </c>
+      <c r="I54" s="3">
+        <v>14200</v>
+      </c>
+      <c r="J54" s="3">
         <v>13500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>12600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>12500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>9500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>9700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>9000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>12900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>13400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>10400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>11100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>11500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>11500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>11000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>7100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>8200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>12800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>9500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>12000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>11000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5191,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,151 +5229,159 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>400</v>
+      </c>
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>500</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
       <c r="P57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q57" s="3">
         <v>600</v>
       </c>
       <c r="R57" s="3">
+        <v>400</v>
+      </c>
+      <c r="S57" s="3">
+        <v>600</v>
+      </c>
+      <c r="T57" s="3">
         <v>900</v>
-      </c>
-      <c r="S57" s="3">
-        <v>900</v>
-      </c>
-      <c r="T57" s="3">
-        <v>700</v>
       </c>
       <c r="U57" s="3">
         <v>900</v>
       </c>
       <c r="V57" s="3">
+        <v>700</v>
+      </c>
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>800</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>800</v>
       </c>
       <c r="AA57" s="3">
         <v>800</v>
       </c>
       <c r="AB57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD57" s="3">
         <v>700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>3600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>4200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>4300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>4500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>100</v>
+      </c>
+      <c r="O58" s="3">
         <v>1700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1800</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5123,11 +5391,11 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5151,10 +5419,10 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>1000</v>
@@ -5162,79 +5430,85 @@
       <c r="AG58" s="3">
         <v>1000</v>
       </c>
-      <c r="AH58" s="3" t="s">
+      <c r="AH58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1400</v>
       </c>
       <c r="N59" s="3">
         <v>1700</v>
       </c>
       <c r="O59" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="P59" s="3">
         <v>1700</v>
       </c>
       <c r="Q59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S59" s="3">
         <v>1600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1100</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>1200</v>
       </c>
       <c r="Z59" s="3">
         <v>1300</v>
@@ -5243,149 +5517,161 @@
         <v>1200</v>
       </c>
       <c r="AB59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD59" s="3">
         <v>1000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2600</v>
-      </c>
-      <c r="U60" s="3">
-        <v>2400</v>
-      </c>
-      <c r="V60" s="3">
-        <v>2500</v>
       </c>
       <c r="W60" s="3">
         <v>2400</v>
       </c>
       <c r="X60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z60" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>2100</v>
       </c>
       <c r="AA60" s="3">
         <v>2000</v>
       </c>
       <c r="AB60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD60" s="3">
         <v>1700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>6000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>6700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>7200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>6800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5403,10 +5689,10 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>2200</v>
@@ -5415,19 +5701,19 @@
         <v>2200</v>
       </c>
       <c r="T61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="U61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="V61" s="3">
         <v>1500</v>
       </c>
       <c r="W61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="X61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="Y61" s="3">
         <v>1600</v>
@@ -5442,123 +5728,135 @@
         <v>1600</v>
       </c>
       <c r="AC61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AE61" s="3">
         <v>1500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2800</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>1900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4500</v>
-      </c>
-      <c r="T62" s="3">
-        <v>4700</v>
-      </c>
-      <c r="U62" s="3">
-        <v>4300</v>
       </c>
       <c r="V62" s="3">
         <v>4700</v>
       </c>
       <c r="W62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="X62" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Y62" s="3">
         <v>2000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2900</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>1000</v>
       </c>
       <c r="AC62" s="3">
         <v>1100</v>
       </c>
       <c r="AD62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF62" s="3">
         <v>1600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>2900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>3300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5953,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +6057,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6161,118 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="E66" s="3">
         <v>3100</v>
       </c>
       <c r="F66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H66" s="3">
         <v>3900</v>
-      </c>
-      <c r="G66" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>3800</v>
       </c>
       <c r="I66" s="3">
         <v>3800</v>
       </c>
       <c r="J66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L66" s="3">
         <v>5100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>7700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>8800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>8200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>8700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>6000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>5900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>6100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>6500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>4700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>4200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>4900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>10200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>11600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>12900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>10200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6307,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6407,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6511,14 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6615,14 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6719,118 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F72" s="3">
         <v>4000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-6000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-6500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-6900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-7200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-8500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-8600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-8700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-8700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-4200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-4200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-4500</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-3800</v>
       </c>
       <c r="Z72" s="3">
         <v>-4000</v>
       </c>
       <c r="AA72" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AC72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6927,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +7031,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +7135,118 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F76" s="3">
         <v>11800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>10900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>500</v>
       </c>
-      <c r="T76" s="3">
-        <v>100</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
+        <v>100</v>
+      </c>
+      <c r="W76" s="3">
         <v>4700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>6300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>2600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7343,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45375</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45284</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45193</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45102</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45011</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44920</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44829</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44738</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44647</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44556</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44374</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44283</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44192</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44101</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44010</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43919</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43828</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43737</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43548</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43457</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43366</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43275</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43184</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43093</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43002</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42911</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42820</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42729</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>900</v>
+      </c>
+      <c r="F81" s="3">
         <v>700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>400</v>
       </c>
       <c r="G81" s="3">
         <v>600</v>
       </c>
       <c r="H81" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I81" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J81" s="3">
         <v>300</v>
       </c>
       <c r="K81" s="3">
+        <v>300</v>
+      </c>
+      <c r="L81" s="3">
+        <v>300</v>
+      </c>
+      <c r="M81" s="3">
         <v>6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>100</v>
-      </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T81" s="3">
+        <v>100</v>
+      </c>
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-4500</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>3300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7598,10 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7229,10 +7627,10 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7265,10 +7663,10 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -7283,25 +7681,31 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AD83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
         <v>300</v>
       </c>
       <c r="AF83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH83" s="3">
         <v>600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7802,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7906,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +8010,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +8114,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8218,118 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
-        <v>100</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>500</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-2400</v>
       </c>
       <c r="AD89" s="3">
         <v>-1000</v>
       </c>
       <c r="AE89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,13 +8364,15 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7939,38 +8381,38 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -7999,31 +8441,37 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8568,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,53 +8672,59 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-4800</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>200</v>
       </c>
-      <c r="L94" s="3">
-        <v>100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -8287,37 +8747,43 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>600</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8818,33 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8918,14 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +9022,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +9126,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,76 +9230,82 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>3600</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -8822,51 +9314,57 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>4900</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>2900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>1000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8940,102 +9438,114 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>3400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>3500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>RAVE</t>
   </si>
@@ -656,267 +656,273 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45375</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45284</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45193</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45102</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45011</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44920</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44829</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44647</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44556</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44374</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44283</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44192</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44101</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44010</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43919</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43828</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43737</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43548</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43457</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43366</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43275</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43184</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43093</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43002</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42911</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42820</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42729</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3000</v>
       </c>
-      <c r="G8" s="3">
-        <v>2800</v>
-      </c>
       <c r="H8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I8" s="3">
         <v>3100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3000</v>
       </c>
       <c r="J8" s="3">
         <v>3000</v>
       </c>
       <c r="K8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L8" s="3">
         <v>2900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>3100</v>
       </c>
       <c r="Z8" s="3">
         <v>3100</v>
       </c>
       <c r="AA8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>3200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>800</v>
+      </c>
+      <c r="E9" s="3">
         <v>1000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>800</v>
       </c>
       <c r="F9" s="3">
         <v>800</v>
@@ -925,37 +931,37 @@
         <v>800</v>
       </c>
       <c r="H9" s="3">
+        <v>800</v>
+      </c>
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>8</v>
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
         <v>100</v>
@@ -976,13 +982,13 @@
         <v>100</v>
       </c>
       <c r="Y9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3">
         <v>400</v>
       </c>
       <c r="AA9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AB9" s="3">
         <v>200</v>
@@ -991,132 +997,138 @@
         <v>200</v>
       </c>
       <c r="AD9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE9" s="3">
         <v>300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1900</v>
       </c>
       <c r="H10" s="3">
         <v>1900</v>
       </c>
       <c r="I10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>2600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>2400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2800</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>2700</v>
       </c>
       <c r="Z10" s="3">
         <v>2700</v>
       </c>
       <c r="AA10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AB10" s="3">
         <v>3000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1381,14 +1400,14 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1406,11 +1425,11 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1421,63 +1440,66 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
-        <v>100</v>
-      </c>
       <c r="Y14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>200</v>
       </c>
       <c r="AA14" s="3">
         <v>200</v>
       </c>
       <c r="AB14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="3">
         <v>100</v>
       </c>
       <c r="AE14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="AF14" s="3">
-        <v>100</v>
-      </c>
       <c r="AG14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH14" s="3">
         <v>800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1498,7 +1520,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1534,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3">
         <v>100</v>
@@ -1552,7 +1574,7 @@
         <v>100</v>
       </c>
       <c r="AE15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AF15" s="3">
         <v>300</v>
@@ -1561,16 +1583,19 @@
         <v>300</v>
       </c>
       <c r="AH15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI15" s="3">
         <v>600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2200</v>
       </c>
       <c r="F17" s="3">
         <v>2200</v>
       </c>
       <c r="G17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>2800</v>
       </c>
       <c r="AB17" s="3">
         <v>2800</v>
       </c>
       <c r="AC17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AD17" s="3">
         <v>2900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>700</v>
+      </c>
+      <c r="E18" s="3">
         <v>600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>500</v>
       </c>
       <c r="H18" s="3">
         <v>500</v>
       </c>
       <c r="I18" s="3">
+        <v>500</v>
+      </c>
+      <c r="J18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>400</v>
       </c>
       <c r="M18" s="3">
         <v>400</v>
       </c>
       <c r="N18" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O18" s="3">
         <v>500</v>
       </c>
       <c r="P18" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q18" s="3">
         <v>300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>400</v>
       </c>
-      <c r="S18" s="3">
-        <v>100</v>
-      </c>
       <c r="T18" s="3">
         <v>100</v>
       </c>
       <c r="U18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-400</v>
       </c>
       <c r="AE18" s="3">
         <v>-400</v>
       </c>
       <c r="AF18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,18 +1909,18 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1954,8 +1987,11 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1963,22 +1999,22 @@
         <v>700</v>
       </c>
       <c r="E21" s="3">
+        <v>700</v>
+      </c>
+      <c r="F21" s="3">
         <v>1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>600</v>
       </c>
       <c r="H21" s="3">
         <v>600</v>
       </c>
       <c r="I21" s="3">
+        <v>600</v>
+      </c>
+      <c r="J21" s="3">
         <v>900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>500</v>
       </c>
       <c r="K21" s="3">
         <v>500</v>
@@ -1987,26 +2023,26 @@
         <v>500</v>
       </c>
       <c r="M21" s="3">
+        <v>500</v>
+      </c>
+      <c r="N21" s="3">
         <v>1200</v>
-      </c>
-      <c r="N21" s="3">
-        <v>500</v>
       </c>
       <c r="O21" s="3">
         <v>500</v>
       </c>
       <c r="P21" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q21" s="3">
         <v>300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>500</v>
       </c>
-      <c r="S21" s="3">
-        <v>100</v>
-      </c>
       <c r="T21" s="3">
         <v>100</v>
       </c>
@@ -2014,52 +2050,55 @@
         <v>100</v>
       </c>
       <c r="V21" s="3">
+        <v>100</v>
+      </c>
+      <c r="W21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
-        <v>100</v>
-      </c>
       <c r="X21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y21" s="3">
         <v>400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>300</v>
       </c>
-      <c r="AC21" s="3">
-        <v>100</v>
-      </c>
       <c r="AD21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2078,14 +2117,14 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,136 +2201,142 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>800</v>
+      </c>
+      <c r="E23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>500</v>
       </c>
       <c r="H23" s="3">
         <v>500</v>
       </c>
       <c r="I23" s="3">
+        <v>500</v>
+      </c>
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>500</v>
       </c>
       <c r="O23" s="3">
         <v>500</v>
       </c>
       <c r="P23" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q23" s="3">
         <v>300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
-        <v>100</v>
-      </c>
       <c r="T23" s="3">
         <v>100</v>
       </c>
       <c r="U23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
       <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
@@ -2299,11 +2344,11 @@
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>-5700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -2326,32 +2371,32 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>4000</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,31 +2522,34 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>300</v>
       </c>
       <c r="K26" s="3">
         <v>300</v>
@@ -2507,102 +2558,105 @@
         <v>300</v>
       </c>
       <c r="M26" s="3">
+        <v>300</v>
+      </c>
+      <c r="N26" s="3">
         <v>6800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>500</v>
       </c>
       <c r="O26" s="3">
         <v>500</v>
       </c>
       <c r="P26" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q26" s="3">
         <v>300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
-        <v>100</v>
-      </c>
       <c r="T26" s="3">
         <v>100</v>
       </c>
       <c r="U26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-4500</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>200</v>
       </c>
-      <c r="AB26" s="3">
-        <v>100</v>
-      </c>
       <c r="AC26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>3300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>300</v>
       </c>
       <c r="K27" s="3">
         <v>300</v>
@@ -2611,79 +2665,82 @@
         <v>300</v>
       </c>
       <c r="M27" s="3">
+        <v>300</v>
+      </c>
+      <c r="N27" s="3">
         <v>6800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>500</v>
       </c>
       <c r="O27" s="3">
         <v>500</v>
       </c>
       <c r="P27" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q27" s="3">
         <v>300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
-        <v>100</v>
-      </c>
       <c r="T27" s="3">
         <v>100</v>
       </c>
       <c r="U27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-4500</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
-      <c r="AB27" s="3">
-        <v>100</v>
-      </c>
       <c r="AC27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>3300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2848,14 +2908,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2867,31 +2927,34 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="3">
         <v>-200</v>
       </c>
       <c r="AG29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AH29" s="3">
         <v>-300</v>
       </c>
       <c r="AI29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,18 +3193,18 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3202,31 +3271,34 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>300</v>
       </c>
       <c r="K33" s="3">
         <v>300</v>
@@ -3235,79 +3307,82 @@
         <v>300</v>
       </c>
       <c r="M33" s="3">
+        <v>300</v>
+      </c>
+      <c r="N33" s="3">
         <v>6800</v>
-      </c>
-      <c r="N33" s="3">
-        <v>500</v>
       </c>
       <c r="O33" s="3">
         <v>500</v>
       </c>
       <c r="P33" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q33" s="3">
         <v>300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
-        <v>100</v>
-      </c>
       <c r="T33" s="3">
         <v>100</v>
       </c>
       <c r="U33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-4500</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>200</v>
       </c>
-      <c r="AB33" s="3">
-        <v>100</v>
-      </c>
       <c r="AC33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>3300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,31 +3485,34 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>300</v>
       </c>
       <c r="K35" s="3">
         <v>300</v>
@@ -3443,188 +3521,194 @@
         <v>300</v>
       </c>
       <c r="M35" s="3">
+        <v>300</v>
+      </c>
+      <c r="N35" s="3">
         <v>6800</v>
-      </c>
-      <c r="N35" s="3">
-        <v>500</v>
       </c>
       <c r="O35" s="3">
         <v>500</v>
       </c>
       <c r="P35" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q35" s="3">
         <v>300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
-        <v>100</v>
-      </c>
       <c r="T35" s="3">
         <v>100</v>
       </c>
       <c r="U35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-4500</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>200</v>
       </c>
-      <c r="AB35" s="3">
-        <v>100</v>
-      </c>
       <c r="AC35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>3300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45375</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45284</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45193</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45102</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45011</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44920</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44829</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44647</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44556</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44374</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44283</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44192</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44101</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44010</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43919</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43828</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43737</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43548</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43457</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43366</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43275</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43184</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43093</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43002</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42911</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42820</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42729</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,124 +3784,128 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2300</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>1900</v>
       </c>
       <c r="AA41" s="3">
         <v>1900</v>
       </c>
       <c r="AB41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AC41" s="3">
         <v>2000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E42" s="3">
         <v>7100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4900</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3907,112 +3996,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2200</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>2300</v>
       </c>
       <c r="AB43" s="3">
         <v>2300</v>
       </c>
       <c r="AC43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AD43" s="3">
         <v>2500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4101,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="AF44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG44" s="3">
         <v>100</v>
@@ -4110,18 +4205,21 @@
         <v>100</v>
       </c>
       <c r="AI44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ44" s="3">
         <v>200</v>
       </c>
+      <c r="AK44" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -4157,7 +4255,7 @@
         <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
@@ -4166,165 +4264,171 @@
         <v>200</v>
       </c>
       <c r="S45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
       </c>
       <c r="U45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V45" s="3">
         <v>400</v>
       </c>
       <c r="W45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X45" s="3">
         <v>500</v>
       </c>
       <c r="Y45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z45" s="3">
         <v>600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>900</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>800</v>
       </c>
       <c r="AC45" s="3">
         <v>800</v>
       </c>
       <c r="AD45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E46" s="3">
         <v>10300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8700</v>
-      </c>
-      <c r="T46" s="3">
-        <v>4900</v>
       </c>
       <c r="U46" s="3">
         <v>4900</v>
       </c>
       <c r="V46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="W46" s="3">
         <v>4000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,8 +4453,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>400</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>400</v>
@@ -4359,7 +4463,7 @@
         <v>400</v>
       </c>
       <c r="N47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O47" s="3">
         <v>500</v>
@@ -4368,7 +4472,7 @@
         <v>500</v>
       </c>
       <c r="Q47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="R47" s="3">
         <v>300</v>
@@ -4377,162 +4481,168 @@
         <v>300</v>
       </c>
       <c r="T47" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="U47" s="3">
         <v>700</v>
       </c>
       <c r="V47" s="3">
+        <v>700</v>
+      </c>
+      <c r="W47" s="3">
         <v>400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>1200</v>
       </c>
       <c r="AA47" s="3">
         <v>1200</v>
       </c>
       <c r="AB47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>300</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
-      </c>
       <c r="AF47" s="3">
         <v>0</v>
       </c>
       <c r="AG47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH47" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI47" s="3">
         <v>200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800</v>
+      </c>
+      <c r="E48" s="3">
         <v>900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4540,7 +4650,7 @@
         <v>200</v>
       </c>
       <c r="E49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F49" s="3">
         <v>300</v>
@@ -4564,7 +4674,7 @@
         <v>300</v>
       </c>
       <c r="M49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N49" s="3">
         <v>200</v>
@@ -4579,7 +4689,7 @@
         <v>200</v>
       </c>
       <c r="R49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S49" s="3">
         <v>100</v>
@@ -4588,7 +4698,7 @@
         <v>100</v>
       </c>
       <c r="U49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V49" s="3">
         <v>200</v>
@@ -4623,8 +4733,8 @@
       <c r="AF49" s="3">
         <v>200</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
+      <c r="AG49" s="3">
+        <v>200</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4869,17 +4988,17 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>5600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>5800</v>
       </c>
       <c r="M52" s="3">
         <v>5800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
+      <c r="N52" s="3">
+        <v>5800</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>8</v>
@@ -4887,8 +5006,8 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -4903,31 +5022,31 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>200</v>
-      </c>
-      <c r="W52" s="3">
-        <v>4200</v>
       </c>
       <c r="X52" s="3">
         <v>4200</v>
       </c>
       <c r="Y52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z52" s="3">
         <v>4300</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>3600</v>
       </c>
       <c r="AA52" s="3">
         <v>3600</v>
       </c>
       <c r="AB52" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AC52" s="3">
         <v>3700</v>
       </c>
       <c r="AD52" s="3">
-        <v>200</v>
+        <v>3700</v>
       </c>
       <c r="AE52" s="3">
         <v>200</v>
@@ -4936,19 +5055,22 @@
         <v>200</v>
       </c>
       <c r="AG52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AH52" s="3">
         <v>500</v>
       </c>
       <c r="AI52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E54" s="3">
         <v>16300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11100</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>11500</v>
       </c>
       <c r="AB54" s="3">
         <v>11500</v>
       </c>
       <c r="AC54" s="3">
+        <v>11500</v>
+      </c>
+      <c r="AD54" s="3">
         <v>11000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,82 +5360,83 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E57" s="3">
         <v>400</v>
       </c>
       <c r="F57" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="G57" s="3">
         <v>700</v>
       </c>
       <c r="H57" s="3">
+        <v>700</v>
+      </c>
+      <c r="I57" s="3">
         <v>600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>500</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
       </c>
       <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>700</v>
       </c>
       <c r="M57" s="3">
         <v>700</v>
       </c>
       <c r="N57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
       <c r="P57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
-      </c>
-      <c r="T57" s="3">
-        <v>900</v>
       </c>
       <c r="U57" s="3">
         <v>900</v>
       </c>
       <c r="V57" s="3">
+        <v>900</v>
+      </c>
+      <c r="W57" s="3">
         <v>700</v>
-      </c>
-      <c r="W57" s="3">
-        <v>900</v>
       </c>
       <c r="X57" s="3">
         <v>900</v>
       </c>
       <c r="Y57" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>800</v>
       </c>
       <c r="AB57" s="3">
         <v>800</v>
@@ -5315,28 +5445,31 @@
         <v>800</v>
       </c>
       <c r="AD57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE57" s="3">
         <v>700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5356,13 +5489,13 @@
         <v>400</v>
       </c>
       <c r="I58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J58" s="3">
         <v>500</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5371,20 +5504,20 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
         <v>1700</v>
       </c>
       <c r="Q58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R58" s="3">
         <v>1800</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5397,8 +5530,8 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5425,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="AF58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG58" s="3">
         <v>1000</v>
@@ -5436,22 +5569,25 @@
       <c r="AI58" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ58" s="3" t="s">
+      <c r="AJ58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>200</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
@@ -5460,222 +5596,228 @@
         <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
         <v>300</v>
       </c>
       <c r="K59" s="3">
+        <v>300</v>
+      </c>
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1600</v>
       </c>
       <c r="T59" s="3">
         <v>1600</v>
       </c>
       <c r="U59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>1000</v>
       </c>
       <c r="AE59" s="3">
         <v>1000</v>
       </c>
       <c r="AF59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG59" s="3">
         <v>1400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1900</v>
-      </c>
-      <c r="AI59" s="3">
-        <v>1400</v>
       </c>
       <c r="AJ59" s="3">
         <v>1400</v>
       </c>
+      <c r="AK59" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="E60" s="3">
         <v>2000</v>
       </c>
       <c r="F60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>2500</v>
       </c>
       <c r="U60" s="3">
         <v>2500</v>
       </c>
       <c r="V60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="W60" s="3">
         <v>2600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
-      </c>
-      <c r="E61" s="3">
-        <v>600</v>
       </c>
       <c r="F61" s="3">
         <v>600</v>
       </c>
       <c r="G61" s="3">
+        <v>600</v>
+      </c>
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5695,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>2200</v>
@@ -5707,7 +5849,7 @@
         <v>2200</v>
       </c>
       <c r="V61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="W61" s="3">
         <v>1500</v>
@@ -5716,7 +5858,7 @@
         <v>1500</v>
       </c>
       <c r="Y61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="Z61" s="3">
         <v>1600</v>
@@ -5734,25 +5876,28 @@
         <v>1600</v>
       </c>
       <c r="AE61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AF61" s="3">
         <v>1500</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>2700</v>
       </c>
       <c r="AG61" s="3">
         <v>2700</v>
       </c>
       <c r="AH61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AI61" s="3">
         <v>2800</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,86 +5922,89 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>1900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,28 +6321,31 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>3800</v>
       </c>
       <c r="J66" s="3">
         <v>3800</v>
@@ -6197,82 +6354,85 @@
         <v>3800</v>
       </c>
       <c r="L66" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="M66" s="3">
         <v>5100</v>
       </c>
       <c r="N66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O66" s="3">
         <v>4700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-8700</v>
       </c>
       <c r="V72" s="3">
         <v>-8700</v>
       </c>
       <c r="W72" s="3">
-        <v>-4200</v>
+        <v>-8700</v>
       </c>
       <c r="X72" s="3">
         <v>-4200</v>
       </c>
       <c r="Y72" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E76" s="3">
         <v>13300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>500</v>
       </c>
-      <c r="V76" s="3">
-        <v>100</v>
-      </c>
       <c r="W76" s="3">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="X76" s="3">
         <v>4700</v>
       </c>
       <c r="Y76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Z76" s="3">
         <v>4400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,140 +7537,146 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45375</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45284</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45193</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45102</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45011</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44920</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44829</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44647</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44556</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44374</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44283</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44192</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44101</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44010</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43919</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43828</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43737</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43548</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43457</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43366</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43275</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43184</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43093</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43002</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42911</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42820</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42729</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>300</v>
       </c>
       <c r="K81" s="3">
         <v>300</v>
@@ -7491,79 +7685,82 @@
         <v>300</v>
       </c>
       <c r="M81" s="3">
+        <v>300</v>
+      </c>
+      <c r="N81" s="3">
         <v>6800</v>
-      </c>
-      <c r="N81" s="3">
-        <v>500</v>
       </c>
       <c r="O81" s="3">
         <v>500</v>
       </c>
       <c r="P81" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q81" s="3">
         <v>300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
-        <v>100</v>
-      </c>
       <c r="T81" s="3">
         <v>100</v>
       </c>
       <c r="U81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-4500</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>200</v>
       </c>
-      <c r="AB81" s="3">
-        <v>100</v>
-      </c>
       <c r="AC81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>3300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7633,7 +7831,7 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7669,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -7687,7 +7885,7 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
         <v>300</v>
@@ -7696,16 +7894,19 @@
         <v>300</v>
       </c>
       <c r="AH83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI83" s="3">
         <v>600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>700</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>400</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-500</v>
       </c>
       <c r="W89" s="3">
         <v>-500</v>
       </c>
       <c r="X89" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="Y89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,16 +8585,17 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -8393,7 +8613,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -8402,7 +8622,7 @@
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -8411,11 +8631,11 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -8447,31 +8667,34 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-300</v>
       </c>
       <c r="AH91" s="3">
         <v>-300</v>
       </c>
       <c r="AI91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,20 +8904,23 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4800</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -8699,35 +8928,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3">
-        <v>100</v>
-      </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -8753,37 +8982,40 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>600</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
       <c r="AI94" s="3">
         <v>0</v>
       </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,68 +9478,71 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-3600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1600</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>3600</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -9305,10 +9550,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -9320,28 +9565,31 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4900</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>2900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1800</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>3400</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>RAVE</t>
   </si>
@@ -656,265 +656,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45375</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45284</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45193</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45102</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45011</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44920</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44829</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44738</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44647</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44556</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44374</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44283</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44192</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44101</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44010</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43919</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43828</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43737</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43548</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43457</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43366</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43275</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43184</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43093</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43002</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42911</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42820</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42729</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>3000</v>
       </c>
       <c r="K8" s="3">
         <v>3000</v>
       </c>
       <c r="L8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M8" s="3">
         <v>2900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>3100</v>
       </c>
       <c r="AA8" s="3">
         <v>3100</v>
       </c>
       <c r="AB8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -922,10 +929,10 @@
         <v>800</v>
       </c>
       <c r="E9" s="3">
+        <v>800</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>800</v>
       </c>
       <c r="G9" s="3">
         <v>800</v>
@@ -934,37 +941,37 @@
         <v>800</v>
       </c>
       <c r="I9" s="3">
+        <v>800</v>
+      </c>
+      <c r="J9" s="3">
         <v>1200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>8</v>
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
         <v>100</v>
@@ -985,13 +992,13 @@
         <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
         <v>400</v>
       </c>
       <c r="AB9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AC9" s="3">
         <v>200</v>
@@ -1000,135 +1007,141 @@
         <v>200</v>
       </c>
       <c r="AE9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF9" s="3">
         <v>300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1900</v>
       </c>
       <c r="I10" s="3">
         <v>1900</v>
       </c>
       <c r="J10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K10" s="3">
         <v>2100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>2600</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>2400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2800</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>2700</v>
       </c>
       <c r="AA10" s="3">
         <v>2700</v>
       </c>
       <c r="AB10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AC10" s="3">
         <v>3000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1403,14 +1423,14 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1428,11 +1448,11 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-700</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1443,66 +1463,69 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
-        <v>100</v>
-      </c>
       <c r="Z14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>200</v>
       </c>
       <c r="AB14" s="3">
         <v>200</v>
       </c>
       <c r="AC14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <v>100</v>
       </c>
       <c r="AF14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="3">
         <v>500</v>
       </c>
-      <c r="AG14" s="3">
-        <v>100</v>
-      </c>
       <c r="AH14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI14" s="3">
         <v>800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1523,7 +1546,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1559,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3">
         <v>100</v>
@@ -1577,7 +1600,7 @@
         <v>100</v>
       </c>
       <c r="AF15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AG15" s="3">
         <v>300</v>
@@ -1586,16 +1609,19 @@
         <v>300</v>
       </c>
       <c r="AI15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2200</v>
       </c>
       <c r="G17" s="3">
         <v>2200</v>
       </c>
       <c r="H17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>2800</v>
       </c>
       <c r="AC17" s="3">
         <v>2800</v>
       </c>
       <c r="AD17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AE17" s="3">
         <v>2900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>14300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>900</v>
+      </c>
+      <c r="E18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>500</v>
       </c>
       <c r="I18" s="3">
         <v>500</v>
       </c>
       <c r="J18" s="3">
+        <v>500</v>
+      </c>
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>400</v>
       </c>
       <c r="N18" s="3">
         <v>400</v>
       </c>
       <c r="O18" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P18" s="3">
         <v>500</v>
       </c>
       <c r="Q18" s="3">
+        <v>500</v>
+      </c>
+      <c r="R18" s="3">
         <v>300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="T18" s="3">
-        <v>100</v>
-      </c>
       <c r="U18" s="3">
         <v>100</v>
       </c>
       <c r="V18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-400</v>
       </c>
       <c r="AF18" s="3">
         <v>-400</v>
       </c>
       <c r="AG18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,18 +1946,18 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1990,34 +2024,37 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E21" s="3">
         <v>700</v>
       </c>
       <c r="F21" s="3">
+        <v>700</v>
+      </c>
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>600</v>
       </c>
       <c r="I21" s="3">
         <v>600</v>
       </c>
       <c r="J21" s="3">
+        <v>600</v>
+      </c>
+      <c r="K21" s="3">
         <v>900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>500</v>
       </c>
       <c r="L21" s="3">
         <v>500</v>
@@ -2026,26 +2063,26 @@
         <v>500</v>
       </c>
       <c r="N21" s="3">
+        <v>500</v>
+      </c>
+      <c r="O21" s="3">
         <v>1200</v>
-      </c>
-      <c r="O21" s="3">
-        <v>500</v>
       </c>
       <c r="P21" s="3">
         <v>500</v>
       </c>
       <c r="Q21" s="3">
+        <v>500</v>
+      </c>
+      <c r="R21" s="3">
         <v>300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>500</v>
       </c>
-      <c r="T21" s="3">
-        <v>100</v>
-      </c>
       <c r="U21" s="3">
         <v>100</v>
       </c>
@@ -2053,52 +2090,55 @@
         <v>100</v>
       </c>
       <c r="W21" s="3">
+        <v>100</v>
+      </c>
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
-        <v>100</v>
-      </c>
       <c r="Y21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>300</v>
       </c>
-      <c r="AD21" s="3">
-        <v>100</v>
-      </c>
       <c r="AE21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2120,14 +2160,14 @@
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,142 +2244,148 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>500</v>
       </c>
       <c r="I23" s="3">
         <v>500</v>
       </c>
       <c r="J23" s="3">
+        <v>500</v>
+      </c>
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>500</v>
       </c>
       <c r="P23" s="3">
         <v>500</v>
       </c>
       <c r="Q23" s="3">
+        <v>500</v>
+      </c>
+      <c r="R23" s="3">
         <v>300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
-        <v>100</v>
-      </c>
       <c r="U23" s="3">
         <v>100</v>
       </c>
       <c r="V23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
-        <v>100</v>
-      </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
@@ -2347,11 +2393,11 @@
         <v>100</v>
       </c>
       <c r="N24" s="3">
+        <v>100</v>
+      </c>
+      <c r="O24" s="3">
         <v>-5700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -2374,32 +2420,32 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="3">
         <v>100</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,34 +2574,37 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>600</v>
-      </c>
-      <c r="K26" s="3">
-        <v>300</v>
       </c>
       <c r="L26" s="3">
         <v>300</v>
@@ -2561,105 +2613,108 @@
         <v>300</v>
       </c>
       <c r="N26" s="3">
+        <v>300</v>
+      </c>
+      <c r="O26" s="3">
         <v>6800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>500</v>
       </c>
       <c r="P26" s="3">
         <v>500</v>
       </c>
       <c r="Q26" s="3">
+        <v>500</v>
+      </c>
+      <c r="R26" s="3">
         <v>300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
-        <v>100</v>
-      </c>
       <c r="U26" s="3">
         <v>100</v>
       </c>
       <c r="V26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-4500</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>200</v>
       </c>
-      <c r="AC26" s="3">
-        <v>100</v>
-      </c>
       <c r="AD26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>3300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>600</v>
-      </c>
-      <c r="K27" s="3">
-        <v>300</v>
       </c>
       <c r="L27" s="3">
         <v>300</v>
@@ -2668,79 +2723,82 @@
         <v>300</v>
       </c>
       <c r="N27" s="3">
+        <v>300</v>
+      </c>
+      <c r="O27" s="3">
         <v>6800</v>
-      </c>
-      <c r="O27" s="3">
-        <v>500</v>
       </c>
       <c r="P27" s="3">
         <v>500</v>
       </c>
       <c r="Q27" s="3">
+        <v>500</v>
+      </c>
+      <c r="R27" s="3">
         <v>300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
-        <v>100</v>
-      </c>
       <c r="U27" s="3">
         <v>100</v>
       </c>
       <c r="V27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-4500</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>200</v>
       </c>
-      <c r="AC27" s="3">
-        <v>100</v>
-      </c>
       <c r="AD27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>3300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2911,14 +2972,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2930,31 +2991,34 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AG29" s="3">
         <v>-200</v>
       </c>
       <c r="AH29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AI29" s="3">
         <v>-300</v>
       </c>
       <c r="AJ29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-400</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,18 +3266,18 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3274,34 +3344,37 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>600</v>
-      </c>
-      <c r="K33" s="3">
-        <v>300</v>
       </c>
       <c r="L33" s="3">
         <v>300</v>
@@ -3310,79 +3383,82 @@
         <v>300</v>
       </c>
       <c r="N33" s="3">
+        <v>300</v>
+      </c>
+      <c r="O33" s="3">
         <v>6800</v>
-      </c>
-      <c r="O33" s="3">
-        <v>500</v>
       </c>
       <c r="P33" s="3">
         <v>500</v>
       </c>
       <c r="Q33" s="3">
+        <v>500</v>
+      </c>
+      <c r="R33" s="3">
         <v>300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
-        <v>100</v>
-      </c>
       <c r="U33" s="3">
         <v>100</v>
       </c>
       <c r="V33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-4500</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AC33" s="3">
-        <v>100</v>
-      </c>
       <c r="AD33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>3300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,34 +3564,37 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>600</v>
-      </c>
-      <c r="K35" s="3">
-        <v>300</v>
       </c>
       <c r="L35" s="3">
         <v>300</v>
@@ -3524,191 +3603,197 @@
         <v>300</v>
       </c>
       <c r="N35" s="3">
+        <v>300</v>
+      </c>
+      <c r="O35" s="3">
         <v>6800</v>
-      </c>
-      <c r="O35" s="3">
-        <v>500</v>
       </c>
       <c r="P35" s="3">
         <v>500</v>
       </c>
       <c r="Q35" s="3">
+        <v>500</v>
+      </c>
+      <c r="R35" s="3">
         <v>300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
-        <v>100</v>
-      </c>
       <c r="U35" s="3">
         <v>100</v>
       </c>
       <c r="V35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-4500</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AC35" s="3">
-        <v>100</v>
-      </c>
       <c r="AD35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>3300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45375</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45284</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45193</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45102</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45011</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44920</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44829</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44738</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44647</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44556</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44374</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44283</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44192</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44101</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44010</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43919</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43828</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43737</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43548</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43457</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43366</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43275</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43184</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43093</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43002</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42911</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42820</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42729</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,130 +3871,134 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2300</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>1900</v>
       </c>
       <c r="AB41" s="3">
         <v>1900</v>
       </c>
       <c r="AC41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AD41" s="3">
         <v>2000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4900</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -3999,115 +4089,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2200</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>2300</v>
       </c>
       <c r="AC43" s="3">
         <v>2300</v>
       </c>
       <c r="AD43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AE43" s="3">
         <v>2500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4199,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="AG44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH44" s="3">
         <v>100</v>
@@ -4208,13 +4304,16 @@
         <v>100</v>
       </c>
       <c r="AJ44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AK44" s="3">
         <v>200</v>
       </c>
+      <c r="AL44" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4222,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -4258,7 +4357,7 @@
         <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
@@ -4267,168 +4366,174 @@
         <v>200</v>
       </c>
       <c r="T45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="U45" s="3">
         <v>500</v>
       </c>
       <c r="V45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W45" s="3">
         <v>400</v>
       </c>
       <c r="X45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y45" s="3">
         <v>500</v>
       </c>
       <c r="Z45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA45" s="3">
         <v>600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>900</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>800</v>
       </c>
       <c r="AD45" s="3">
         <v>800</v>
       </c>
       <c r="AE45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E46" s="3">
         <v>10400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8700</v>
-      </c>
-      <c r="U46" s="3">
-        <v>4900</v>
       </c>
       <c r="V46" s="3">
         <v>4900</v>
       </c>
       <c r="W46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="X46" s="3">
         <v>4000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4456,8 +4561,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>400</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>400</v>
@@ -4466,7 +4571,7 @@
         <v>400</v>
       </c>
       <c r="O47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P47" s="3">
         <v>500</v>
@@ -4475,7 +4580,7 @@
         <v>500</v>
       </c>
       <c r="R47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="S47" s="3">
         <v>300</v>
@@ -4484,165 +4589,171 @@
         <v>300</v>
       </c>
       <c r="U47" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="V47" s="3">
         <v>700</v>
       </c>
       <c r="W47" s="3">
+        <v>700</v>
+      </c>
+      <c r="X47" s="3">
         <v>400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>1200</v>
       </c>
       <c r="AB47" s="3">
         <v>1200</v>
       </c>
       <c r="AC47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD47" s="3">
         <v>1000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>300</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
-      </c>
       <c r="AG47" s="3">
         <v>0</v>
       </c>
       <c r="AH47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4653,7 +4764,7 @@
         <v>200</v>
       </c>
       <c r="F49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G49" s="3">
         <v>300</v>
@@ -4677,7 +4788,7 @@
         <v>300</v>
       </c>
       <c r="N49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O49" s="3">
         <v>200</v>
@@ -4692,7 +4803,7 @@
         <v>200</v>
       </c>
       <c r="S49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T49" s="3">
         <v>100</v>
@@ -4701,7 +4812,7 @@
         <v>100</v>
       </c>
       <c r="V49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W49" s="3">
         <v>200</v>
@@ -4736,8 +4847,8 @@
       <c r="AG49" s="3">
         <v>200</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
+      <c r="AH49" s="3">
+        <v>200</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4991,17 +5111,17 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>5600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>5800</v>
       </c>
       <c r="N52" s="3">
         <v>5800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
+      <c r="O52" s="3">
+        <v>5800</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
@@ -5009,8 +5129,8 @@
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -5025,31 +5145,31 @@
         <v>0</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>200</v>
-      </c>
-      <c r="X52" s="3">
-        <v>4200</v>
       </c>
       <c r="Y52" s="3">
         <v>4200</v>
       </c>
       <c r="Z52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AA52" s="3">
         <v>4300</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>3600</v>
       </c>
       <c r="AB52" s="3">
         <v>3600</v>
       </c>
       <c r="AC52" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AD52" s="3">
         <v>3700</v>
       </c>
       <c r="AE52" s="3">
-        <v>200</v>
+        <v>3700</v>
       </c>
       <c r="AF52" s="3">
         <v>200</v>
@@ -5058,19 +5178,22 @@
         <v>200</v>
       </c>
       <c r="AH52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AI52" s="3">
         <v>500</v>
       </c>
       <c r="AJ52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK52" s="3">
         <v>200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E54" s="3">
         <v>16100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11100</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>11500</v>
       </c>
       <c r="AC54" s="3">
         <v>11500</v>
       </c>
       <c r="AD54" s="3">
+        <v>11500</v>
+      </c>
+      <c r="AE54" s="3">
         <v>11000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,85 +5491,86 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
-      </c>
-      <c r="E57" s="3">
-        <v>400</v>
       </c>
       <c r="F57" s="3">
         <v>400</v>
       </c>
       <c r="G57" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="H57" s="3">
         <v>700</v>
       </c>
       <c r="I57" s="3">
+        <v>700</v>
+      </c>
+      <c r="J57" s="3">
         <v>600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>500</v>
       </c>
       <c r="K57" s="3">
         <v>500</v>
       </c>
       <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
         <v>600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>700</v>
       </c>
       <c r="N57" s="3">
         <v>700</v>
       </c>
       <c r="O57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P57" s="3">
         <v>600</v>
       </c>
       <c r="Q57" s="3">
+        <v>600</v>
+      </c>
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
-      </c>
-      <c r="U57" s="3">
-        <v>900</v>
       </c>
       <c r="V57" s="3">
         <v>900</v>
       </c>
       <c r="W57" s="3">
+        <v>900</v>
+      </c>
+      <c r="X57" s="3">
         <v>700</v>
-      </c>
-      <c r="X57" s="3">
-        <v>900</v>
       </c>
       <c r="Y57" s="3">
         <v>900</v>
       </c>
       <c r="Z57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA57" s="3">
         <v>1200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>800</v>
       </c>
       <c r="AC57" s="3">
         <v>800</v>
@@ -5448,28 +5579,31 @@
         <v>800</v>
       </c>
       <c r="AE57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF57" s="3">
         <v>700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5492,13 +5626,13 @@
         <v>400</v>
       </c>
       <c r="J58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5507,20 +5641,20 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>1700</v>
       </c>
       <c r="R58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S58" s="3">
         <v>1800</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5533,8 +5667,8 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5561,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH58" s="3">
         <v>1000</v>
@@ -5572,25 +5706,28 @@
       <c r="AJ58" s="3">
         <v>1000</v>
       </c>
-      <c r="AK58" s="3" t="s">
+      <c r="AK58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AL58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>200</v>
       </c>
       <c r="H59" s="3">
         <v>200</v>
@@ -5599,228 +5736,234 @@
         <v>200</v>
       </c>
       <c r="J59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>300</v>
       </c>
       <c r="L59" s="3">
+        <v>300</v>
+      </c>
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1600</v>
       </c>
       <c r="U59" s="3">
         <v>1600</v>
       </c>
       <c r="V59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>1000</v>
       </c>
       <c r="AF59" s="3">
         <v>1000</v>
       </c>
       <c r="AG59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1900</v>
-      </c>
-      <c r="AJ59" s="3">
-        <v>1400</v>
       </c>
       <c r="AK59" s="3">
         <v>1400</v>
       </c>
+      <c r="AL59" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>2000</v>
       </c>
       <c r="F60" s="3">
         <v>2000</v>
       </c>
       <c r="G60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2300</v>
-      </c>
-      <c r="U60" s="3">
-        <v>2500</v>
       </c>
       <c r="V60" s="3">
         <v>2500</v>
       </c>
       <c r="W60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="X60" s="3">
         <v>2600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>500</v>
-      </c>
-      <c r="F61" s="3">
-        <v>600</v>
       </c>
       <c r="G61" s="3">
         <v>600</v>
       </c>
       <c r="H61" s="3">
+        <v>600</v>
+      </c>
+      <c r="I61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5840,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>2200</v>
@@ -5852,7 +5995,7 @@
         <v>2200</v>
       </c>
       <c r="W61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="X61" s="3">
         <v>1500</v>
@@ -5861,7 +6004,7 @@
         <v>1500</v>
       </c>
       <c r="Z61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="AA61" s="3">
         <v>1600</v>
@@ -5879,25 +6022,28 @@
         <v>1600</v>
       </c>
       <c r="AF61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AG61" s="3">
         <v>1500</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>2700</v>
       </c>
       <c r="AH61" s="3">
         <v>2700</v>
       </c>
       <c r="AI61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,86 +6071,89 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>1900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,31 +6479,34 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3800</v>
       </c>
       <c r="K66" s="3">
         <v>3800</v>
@@ -6357,82 +6515,85 @@
         <v>3800</v>
       </c>
       <c r="M66" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="N66" s="3">
         <v>5100</v>
       </c>
       <c r="O66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P66" s="3">
         <v>4700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>10200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E72" s="3">
         <v>6000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-8700</v>
       </c>
       <c r="W72" s="3">
         <v>-8700</v>
       </c>
       <c r="X72" s="3">
-        <v>-4200</v>
+        <v>-8700</v>
       </c>
       <c r="Y72" s="3">
         <v>-4200</v>
       </c>
       <c r="Z72" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E76" s="3">
         <v>13800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>500</v>
       </c>
-      <c r="W76" s="3">
-        <v>100</v>
-      </c>
       <c r="X76" s="3">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="Y76" s="3">
         <v>4700</v>
       </c>
       <c r="Z76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AA76" s="3">
         <v>4400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,146 +7729,152 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45375</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45284</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45193</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45102</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45011</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44920</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44829</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44738</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44647</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44556</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44374</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44283</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44192</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44101</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44010</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43919</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43828</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43737</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43548</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43457</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43366</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43275</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43184</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43093</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43002</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42911</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42820</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42729</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>600</v>
-      </c>
-      <c r="K81" s="3">
-        <v>300</v>
       </c>
       <c r="L81" s="3">
         <v>300</v>
@@ -7688,79 +7883,82 @@
         <v>300</v>
       </c>
       <c r="N81" s="3">
+        <v>300</v>
+      </c>
+      <c r="O81" s="3">
         <v>6800</v>
-      </c>
-      <c r="O81" s="3">
-        <v>500</v>
       </c>
       <c r="P81" s="3">
         <v>500</v>
       </c>
       <c r="Q81" s="3">
+        <v>500</v>
+      </c>
+      <c r="R81" s="3">
         <v>300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
-        <v>100</v>
-      </c>
       <c r="U81" s="3">
         <v>100</v>
       </c>
       <c r="V81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-4500</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AC81" s="3">
-        <v>100</v>
-      </c>
       <c r="AD81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>3300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7834,7 +8033,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -7870,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
@@ -7888,7 +8087,7 @@
         <v>100</v>
       </c>
       <c r="AF83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AG83" s="3">
         <v>300</v>
@@ -7897,16 +8096,19 @@
         <v>300</v>
       </c>
       <c r="AI83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>400</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-500</v>
       </c>
       <c r="X89" s="3">
         <v>-500</v>
       </c>
       <c r="Y89" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="Z89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,19 +8806,20 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -8616,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -8625,7 +8846,7 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -8634,11 +8855,11 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -8670,31 +8891,34 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-300</v>
       </c>
       <c r="AI91" s="3">
         <v>-300</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,23 +9134,26 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4800</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -8931,35 +9161,35 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
-        <v>100</v>
-      </c>
       <c r="P94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -8985,37 +9215,40 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>600</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,71 +9724,74 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-3600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>3600</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -9553,10 +9799,10 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -9568,28 +9814,31 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4900</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1800</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>3400</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>1400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>RAVE</t>
   </si>
@@ -656,294 +656,300 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45375</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45284</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45193</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45102</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45011</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44920</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44829</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44647</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44556</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44374</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44283</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44192</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44101</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44010</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43919</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43828</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43737</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43548</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43457</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43366</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43275</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43184</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43093</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43002</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42911</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42820</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42729</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="E8" s="3">
         <v>3200</v>
       </c>
       <c r="F8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G8" s="3">
         <v>3000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3000</v>
       </c>
       <c r="N8" s="3">
         <v>3000</v>
       </c>
       <c r="O8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P8" s="3">
         <v>2900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2900</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>3100</v>
       </c>
       <c r="AD8" s="3">
         <v>3100</v>
       </c>
       <c r="AE8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AF8" s="3">
         <v>3200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>800</v>
       </c>
       <c r="F9" s="3">
         <v>800</v>
@@ -952,10 +958,10 @@
         <v>800</v>
       </c>
       <c r="H9" s="3">
+        <v>800</v>
+      </c>
+      <c r="I9" s="3">
         <v>1000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>800</v>
       </c>
       <c r="J9" s="3">
         <v>800</v>
@@ -964,37 +970,37 @@
         <v>800</v>
       </c>
       <c r="L9" s="3">
+        <v>800</v>
+      </c>
+      <c r="M9" s="3">
         <v>1200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>8</v>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U9" s="3">
-        <v>0</v>
+      <c r="U9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
@@ -1015,13 +1021,13 @@
         <v>100</v>
       </c>
       <c r="AC9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AD9" s="3">
         <v>400</v>
       </c>
       <c r="AE9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AF9" s="3">
         <v>200</v>
@@ -1030,144 +1036,150 @@
         <v>200</v>
       </c>
       <c r="AH9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI9" s="3">
         <v>300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1900</v>
       </c>
       <c r="L10" s="3">
         <v>1900</v>
       </c>
       <c r="M10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N10" s="3">
         <v>2100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>2600</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3">
         <v>2400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2800</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>2700</v>
       </c>
       <c r="AD10" s="3">
         <v>2700</v>
       </c>
       <c r="AE10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AF10" s="3">
         <v>3000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1472,14 +1491,14 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1497,11 +1516,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-700</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
@@ -1512,52 +1531,55 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AB14" s="3">
-        <v>100</v>
-      </c>
       <c r="AC14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1300</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>200</v>
       </c>
       <c r="AE14" s="3">
         <v>200</v>
       </c>
       <c r="AF14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AG14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="3">
         <v>100</v>
       </c>
       <c r="AI14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>500</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>100</v>
-      </c>
       <c r="AK14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL14" s="3">
         <v>800</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>5100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1571,16 +1593,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1601,7 +1623,7 @@
         <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1637,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="3">
         <v>100</v>
@@ -1655,7 +1677,7 @@
         <v>100</v>
       </c>
       <c r="AI15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AJ15" s="3">
         <v>300</v>
@@ -1664,16 +1686,19 @@
         <v>300</v>
       </c>
       <c r="AL15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM15" s="3">
         <v>600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2200</v>
       </c>
       <c r="J17" s="3">
         <v>2200</v>
       </c>
       <c r="K17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>2800</v>
       </c>
       <c r="AF17" s="3">
         <v>2800</v>
       </c>
       <c r="AG17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AH17" s="3">
         <v>2900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>14300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>700</v>
+      </c>
+      <c r="E18" s="3">
         <v>800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>500</v>
       </c>
       <c r="L18" s="3">
         <v>500</v>
       </c>
       <c r="M18" s="3">
+        <v>500</v>
+      </c>
+      <c r="N18" s="3">
         <v>800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>500</v>
-      </c>
-      <c r="P18" s="3">
-        <v>400</v>
       </c>
       <c r="Q18" s="3">
         <v>400</v>
       </c>
       <c r="R18" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S18" s="3">
         <v>500</v>
       </c>
       <c r="T18" s="3">
+        <v>500</v>
+      </c>
+      <c r="U18" s="3">
         <v>300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3">
-        <v>100</v>
-      </c>
       <c r="X18" s="3">
         <v>100</v>
       </c>
       <c r="Y18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>-400</v>
       </c>
       <c r="AI18" s="3">
         <v>-400</v>
       </c>
       <c r="AJ18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,16 +2017,17 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
@@ -2002,11 +2035,11 @@
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
@@ -2023,18 +2056,18 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -2101,8 +2134,11 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2110,34 +2146,34 @@
         <v>800</v>
       </c>
       <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
         <v>1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>700</v>
       </c>
       <c r="H21" s="3">
         <v>700</v>
       </c>
       <c r="I21" s="3">
+        <v>700</v>
+      </c>
+      <c r="J21" s="3">
         <v>1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>600</v>
       </c>
       <c r="L21" s="3">
         <v>600</v>
       </c>
       <c r="M21" s="3">
+        <v>600</v>
+      </c>
+      <c r="N21" s="3">
         <v>900</v>
-      </c>
-      <c r="N21" s="3">
-        <v>500</v>
       </c>
       <c r="O21" s="3">
         <v>500</v>
@@ -2146,26 +2182,26 @@
         <v>500</v>
       </c>
       <c r="Q21" s="3">
+        <v>500</v>
+      </c>
+      <c r="R21" s="3">
         <v>1200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>500</v>
       </c>
       <c r="S21" s="3">
         <v>500</v>
       </c>
       <c r="T21" s="3">
+        <v>500</v>
+      </c>
+      <c r="U21" s="3">
         <v>300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>500</v>
       </c>
-      <c r="W21" s="3">
-        <v>100</v>
-      </c>
       <c r="X21" s="3">
         <v>100</v>
       </c>
@@ -2173,52 +2209,55 @@
         <v>100</v>
       </c>
       <c r="Z21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="AA21" s="3">
-        <v>100</v>
-      </c>
       <c r="AB21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>300</v>
       </c>
-      <c r="AG21" s="3">
-        <v>100</v>
-      </c>
       <c r="AH21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2249,14 +2288,14 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2333,124 +2372,130 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>800</v>
+      </c>
+      <c r="E23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
-      </c>
-      <c r="K23" s="3">
-        <v>500</v>
       </c>
       <c r="L23" s="3">
         <v>500</v>
       </c>
       <c r="M23" s="3">
+        <v>500</v>
+      </c>
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>500</v>
       </c>
       <c r="S23" s="3">
         <v>500</v>
       </c>
       <c r="T23" s="3">
+        <v>500</v>
+      </c>
+      <c r="U23" s="3">
         <v>300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3">
-        <v>100</v>
-      </c>
       <c r="X23" s="3">
         <v>100</v>
       </c>
       <c r="Y23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
       <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>200</v>
       </c>
-      <c r="AG23" s="3">
-        <v>0</v>
-      </c>
       <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2458,35 +2503,35 @@
         <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>100</v>
-      </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
-        <v>100</v>
-      </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
@@ -2494,11 +2539,11 @@
         <v>100</v>
       </c>
       <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>-5700</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2521,32 +2566,32 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>4000</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="3">
         <v>100</v>
       </c>
       <c r="AG24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
         <v>0</v>
       </c>
@@ -2565,8 +2610,11 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2729,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2690,34 +2741,34 @@
         <v>600</v>
       </c>
       <c r="E26" s="3">
+        <v>600</v>
+      </c>
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
-      </c>
-      <c r="N26" s="3">
-        <v>300</v>
       </c>
       <c r="O26" s="3">
         <v>300</v>
@@ -2726,79 +2777,82 @@
         <v>300</v>
       </c>
       <c r="Q26" s="3">
+        <v>300</v>
+      </c>
+      <c r="R26" s="3">
         <v>6800</v>
-      </c>
-      <c r="R26" s="3">
-        <v>500</v>
       </c>
       <c r="S26" s="3">
         <v>500</v>
       </c>
       <c r="T26" s="3">
+        <v>500</v>
+      </c>
+      <c r="U26" s="3">
         <v>300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="W26" s="3">
-        <v>100</v>
-      </c>
       <c r="X26" s="3">
         <v>100</v>
       </c>
       <c r="Y26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
-      <c r="AF26" s="3">
-        <v>100</v>
-      </c>
       <c r="AG26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>3300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2806,34 +2860,34 @@
         <v>600</v>
       </c>
       <c r="E27" s="3">
+        <v>600</v>
+      </c>
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
-      </c>
-      <c r="N27" s="3">
-        <v>300</v>
       </c>
       <c r="O27" s="3">
         <v>300</v>
@@ -2842,79 +2896,82 @@
         <v>300</v>
       </c>
       <c r="Q27" s="3">
+        <v>300</v>
+      </c>
+      <c r="R27" s="3">
         <v>6800</v>
-      </c>
-      <c r="R27" s="3">
-        <v>500</v>
       </c>
       <c r="S27" s="3">
         <v>500</v>
       </c>
       <c r="T27" s="3">
+        <v>500</v>
+      </c>
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3">
-        <v>100</v>
-      </c>
       <c r="X27" s="3">
         <v>100</v>
       </c>
       <c r="Y27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
-      <c r="AF27" s="3">
-        <v>100</v>
-      </c>
       <c r="AG27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>3300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3103,14 +3163,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3122,31 +3182,34 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AJ29" s="3">
         <v>-200</v>
       </c>
       <c r="AK29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AL29" s="3">
         <v>-300</v>
       </c>
       <c r="AM29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-400</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,16 +3443,19 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -3394,11 +3463,11 @@
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
@@ -3415,18 +3484,18 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3493,8 +3562,11 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3502,34 +3574,34 @@
         <v>600</v>
       </c>
       <c r="E33" s="3">
+        <v>600</v>
+      </c>
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
-      </c>
-      <c r="N33" s="3">
-        <v>300</v>
       </c>
       <c r="O33" s="3">
         <v>300</v>
@@ -3538,79 +3610,82 @@
         <v>300</v>
       </c>
       <c r="Q33" s="3">
+        <v>300</v>
+      </c>
+      <c r="R33" s="3">
         <v>6800</v>
-      </c>
-      <c r="R33" s="3">
-        <v>500</v>
       </c>
       <c r="S33" s="3">
         <v>500</v>
       </c>
       <c r="T33" s="3">
+        <v>500</v>
+      </c>
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3">
-        <v>100</v>
-      </c>
       <c r="X33" s="3">
         <v>100</v>
       </c>
       <c r="Y33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
-      <c r="AF33" s="3">
-        <v>100</v>
-      </c>
       <c r="AG33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>3300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-7900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3800,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3734,34 +3812,34 @@
         <v>600</v>
       </c>
       <c r="E35" s="3">
+        <v>600</v>
+      </c>
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
-      </c>
-      <c r="N35" s="3">
-        <v>300</v>
       </c>
       <c r="O35" s="3">
         <v>300</v>
@@ -3770,200 +3848,206 @@
         <v>300</v>
       </c>
       <c r="Q35" s="3">
+        <v>300</v>
+      </c>
+      <c r="R35" s="3">
         <v>6800</v>
-      </c>
-      <c r="R35" s="3">
-        <v>500</v>
       </c>
       <c r="S35" s="3">
         <v>500</v>
       </c>
       <c r="T35" s="3">
+        <v>500</v>
+      </c>
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3">
-        <v>100</v>
-      </c>
       <c r="X35" s="3">
         <v>100</v>
       </c>
       <c r="Y35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
-      <c r="AF35" s="3">
-        <v>100</v>
-      </c>
       <c r="AG35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>3300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-7900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45375</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45284</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45193</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45102</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45011</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44920</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44829</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44647</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44556</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44374</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44283</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44192</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44101</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44010</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43919</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43828</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43737</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43548</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43457</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43366</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43275</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43184</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43093</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43002</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42911</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42820</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42729</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,148 +4131,152 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2300</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>1900</v>
       </c>
       <c r="AE41" s="3">
         <v>1900</v>
       </c>
       <c r="AF41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AG41" s="3">
         <v>2000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E42" s="3">
         <v>9200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4278,124 +4367,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2200</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>2300</v>
       </c>
       <c r="AF43" s="3">
         <v>2300</v>
       </c>
       <c r="AG43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH43" s="3">
         <v>2500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4496,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK44" s="3">
         <v>100</v>
@@ -4505,13 +4600,16 @@
         <v>100</v>
       </c>
       <c r="AM44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AN44" s="3">
         <v>200</v>
       </c>
+      <c r="AO44" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4522,13 +4620,13 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
         <v>100</v>
@@ -4564,7 +4662,7 @@
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>200</v>
@@ -4573,177 +4671,183 @@
         <v>200</v>
       </c>
       <c r="W45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="X45" s="3">
         <v>500</v>
       </c>
       <c r="Y45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Z45" s="3">
         <v>400</v>
       </c>
       <c r="AA45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AB45" s="3">
         <v>500</v>
       </c>
       <c r="AC45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD45" s="3">
         <v>600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>900</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>800</v>
       </c>
       <c r="AG45" s="3">
         <v>800</v>
       </c>
       <c r="AH45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI45" s="3">
         <v>1000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8700</v>
-      </c>
-      <c r="X46" s="3">
-        <v>4900</v>
       </c>
       <c r="Y46" s="3">
         <v>4900</v>
       </c>
       <c r="Z46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AA46" s="3">
         <v>4000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,8 +4884,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>400</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>400</v>
@@ -4790,7 +4894,7 @@
         <v>400</v>
       </c>
       <c r="R47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S47" s="3">
         <v>500</v>
@@ -4799,7 +4903,7 @@
         <v>500</v>
       </c>
       <c r="U47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="V47" s="3">
         <v>300</v>
@@ -4808,179 +4912,185 @@
         <v>300</v>
       </c>
       <c r="X47" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="Y47" s="3">
         <v>700</v>
       </c>
       <c r="Z47" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA47" s="3">
         <v>400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>1200</v>
       </c>
       <c r="AE47" s="3">
         <v>1200</v>
       </c>
       <c r="AF47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG47" s="3">
         <v>1000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>300</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
       <c r="AK47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL47" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM47" s="3">
         <v>200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>5800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>200</v>
@@ -4995,7 +5105,7 @@
         <v>200</v>
       </c>
       <c r="I49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J49" s="3">
         <v>300</v>
@@ -5019,7 +5129,7 @@
         <v>300</v>
       </c>
       <c r="Q49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R49" s="3">
         <v>200</v>
@@ -5034,7 +5144,7 @@
         <v>200</v>
       </c>
       <c r="V49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W49" s="3">
         <v>100</v>
@@ -5043,7 +5153,7 @@
         <v>100</v>
       </c>
       <c r="Y49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z49" s="3">
         <v>200</v>
@@ -5078,8 +5188,8 @@
       <c r="AJ49" s="3">
         <v>200</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>8</v>
+      <c r="AK49" s="3">
+        <v>200</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>8</v>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5438,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5360,17 +5479,17 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>5600</v>
-      </c>
-      <c r="P52" s="3">
-        <v>5800</v>
       </c>
       <c r="Q52" s="3">
         <v>5800</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
+      <c r="R52" s="3">
+        <v>5800</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
@@ -5378,8 +5497,8 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -5394,31 +5513,31 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>200</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>4200</v>
       </c>
       <c r="AB52" s="3">
         <v>4200</v>
       </c>
       <c r="AC52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AD52" s="3">
         <v>4300</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>3600</v>
       </c>
       <c r="AE52" s="3">
         <v>3600</v>
       </c>
       <c r="AF52" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AG52" s="3">
         <v>3700</v>
       </c>
       <c r="AH52" s="3">
-        <v>200</v>
+        <v>3700</v>
       </c>
       <c r="AI52" s="3">
         <v>200</v>
@@ -5427,19 +5546,22 @@
         <v>200</v>
       </c>
       <c r="AK52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AL52" s="3">
         <v>500</v>
       </c>
       <c r="AM52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AN52" s="3">
         <v>200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E54" s="3">
         <v>17000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11100</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>11500</v>
       </c>
       <c r="AF54" s="3">
         <v>11500</v>
       </c>
       <c r="AG54" s="3">
+        <v>11500</v>
+      </c>
+      <c r="AH54" s="3">
         <v>11000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,94 +5883,95 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>400</v>
       </c>
       <c r="I57" s="3">
         <v>400</v>
       </c>
       <c r="J57" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="K57" s="3">
         <v>700</v>
       </c>
       <c r="L57" s="3">
+        <v>700</v>
+      </c>
+      <c r="M57" s="3">
         <v>600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>500</v>
       </c>
       <c r="N57" s="3">
         <v>500</v>
       </c>
       <c r="O57" s="3">
+        <v>500</v>
+      </c>
+      <c r="P57" s="3">
         <v>600</v>
-      </c>
-      <c r="P57" s="3">
-        <v>700</v>
       </c>
       <c r="Q57" s="3">
         <v>700</v>
       </c>
       <c r="R57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="S57" s="3">
         <v>600</v>
       </c>
       <c r="T57" s="3">
+        <v>600</v>
+      </c>
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
-      </c>
-      <c r="X57" s="3">
-        <v>900</v>
       </c>
       <c r="Y57" s="3">
         <v>900</v>
       </c>
       <c r="Z57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA57" s="3">
         <v>700</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>900</v>
       </c>
       <c r="AB57" s="3">
         <v>900</v>
       </c>
       <c r="AC57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD57" s="3">
         <v>1200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>800</v>
       </c>
       <c r="AF57" s="3">
         <v>800</v>
@@ -5850,28 +5980,31 @@
         <v>800</v>
       </c>
       <c r="AH57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI57" s="3">
         <v>700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5903,13 +6036,13 @@
         <v>400</v>
       </c>
       <c r="M58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N58" s="3">
         <v>500</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5918,20 +6051,20 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>1700</v>
       </c>
       <c r="U58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V58" s="3">
         <v>1800</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5944,8 +6077,8 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5972,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK58" s="3">
         <v>1000</v>
@@ -5983,11 +6116,14 @@
       <c r="AM58" s="3">
         <v>1000</v>
       </c>
-      <c r="AN58" s="3" t="s">
+      <c r="AN58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5995,22 +6131,22 @@
         <v>100</v>
       </c>
       <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
-        <v>100</v>
-      </c>
       <c r="H59" s="3">
+        <v>100</v>
+      </c>
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>200</v>
@@ -6019,246 +6155,252 @@
         <v>200</v>
       </c>
       <c r="M59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
       </c>
       <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
         <v>1300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1700</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1600</v>
       </c>
       <c r="X59" s="3">
         <v>1600</v>
       </c>
       <c r="Y59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>1000</v>
       </c>
       <c r="AI59" s="3">
         <v>1000</v>
       </c>
       <c r="AJ59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK59" s="3">
         <v>1400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1900</v>
-      </c>
-      <c r="AM59" s="3">
-        <v>1400</v>
       </c>
       <c r="AN59" s="3">
         <v>1400</v>
       </c>
+      <c r="AO59" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2000</v>
       </c>
       <c r="I60" s="3">
         <v>2000</v>
       </c>
       <c r="J60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2300</v>
-      </c>
-      <c r="X60" s="3">
-        <v>2500</v>
       </c>
       <c r="Y60" s="3">
         <v>2500</v>
       </c>
       <c r="Z60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AA60" s="3">
         <v>2600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>6800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
-      </c>
-      <c r="I61" s="3">
-        <v>600</v>
       </c>
       <c r="J61" s="3">
         <v>600</v>
       </c>
       <c r="K61" s="3">
+        <v>600</v>
+      </c>
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -6278,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>2200</v>
@@ -6290,7 +6432,7 @@
         <v>2200</v>
       </c>
       <c r="Z61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="AA61" s="3">
         <v>1500</v>
@@ -6299,7 +6441,7 @@
         <v>1500</v>
       </c>
       <c r="AC61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="AD61" s="3">
         <v>1600</v>
@@ -6317,25 +6459,28 @@
         <v>1600</v>
       </c>
       <c r="AI61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>1500</v>
-      </c>
-      <c r="AJ61" s="3">
-        <v>2700</v>
       </c>
       <c r="AK61" s="3">
         <v>2700</v>
       </c>
       <c r="AL61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AM61" s="3">
         <v>2800</v>
       </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,86 +6517,89 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3">
         <v>1900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,40 +6952,43 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2200</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2400</v>
       </c>
       <c r="F66" s="3">
         <v>2400</v>
       </c>
       <c r="G66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H66" s="3">
         <v>2300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3900</v>
-      </c>
-      <c r="M66" s="3">
-        <v>3800</v>
       </c>
       <c r="N66" s="3">
         <v>3800</v>
@@ -6840,82 +6997,85 @@
         <v>3800</v>
       </c>
       <c r="P66" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="Q66" s="3">
         <v>5100</v>
       </c>
       <c r="R66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="S66" s="3">
         <v>4700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>10200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>10200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E72" s="3">
         <v>8300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-8700</v>
       </c>
       <c r="Z72" s="3">
         <v>-8700</v>
       </c>
       <c r="AA72" s="3">
-        <v>-4200</v>
+        <v>-8700</v>
       </c>
       <c r="AB72" s="3">
         <v>-4200</v>
       </c>
       <c r="AC72" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-4800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-1300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E76" s="3">
         <v>14800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>500</v>
       </c>
-      <c r="Z76" s="3">
-        <v>100</v>
-      </c>
       <c r="AA76" s="3">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="AB76" s="3">
         <v>4700</v>
       </c>
       <c r="AC76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AD76" s="3">
         <v>4400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8304,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45375</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45284</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45193</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45102</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45011</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44920</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44829</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44647</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44556</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44374</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44283</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44192</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44101</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44010</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43919</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43828</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43737</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43548</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43457</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43366</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43275</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43184</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43093</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43002</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42911</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42820</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42729</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8246,34 +8440,34 @@
         <v>600</v>
       </c>
       <c r="E81" s="3">
+        <v>600</v>
+      </c>
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
-      </c>
-      <c r="N81" s="3">
-        <v>300</v>
       </c>
       <c r="O81" s="3">
         <v>300</v>
@@ -8282,79 +8476,82 @@
         <v>300</v>
       </c>
       <c r="Q81" s="3">
+        <v>300</v>
+      </c>
+      <c r="R81" s="3">
         <v>6800</v>
-      </c>
-      <c r="R81" s="3">
-        <v>500</v>
       </c>
       <c r="S81" s="3">
         <v>500</v>
       </c>
       <c r="T81" s="3">
+        <v>500</v>
+      </c>
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3">
-        <v>100</v>
-      </c>
       <c r="X81" s="3">
         <v>100</v>
       </c>
       <c r="Y81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
-      <c r="AF81" s="3">
-        <v>100</v>
-      </c>
       <c r="AG81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>3300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-7900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8592,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8440,7 +8638,7 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8476,7 +8674,7 @@
         <v>0</v>
       </c>
       <c r="AC83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
@@ -8494,7 +8692,7 @@
         <v>100</v>
       </c>
       <c r="AI83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AJ83" s="3">
         <v>300</v>
@@ -8503,16 +8701,19 @@
         <v>300</v>
       </c>
       <c r="AL83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM83" s="3">
         <v>600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>400</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-500</v>
       </c>
       <c r="AA89" s="3">
         <v>-500</v>
       </c>
       <c r="AB89" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="AC89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9468,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9266,11 +9486,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -9288,7 +9508,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
@@ -9297,7 +9517,7 @@
         <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -9306,11 +9526,11 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -9342,31 +9562,34 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AK91" s="3">
-        <v>-300</v>
       </c>
       <c r="AL91" s="3">
         <v>-300</v>
       </c>
       <c r="AM91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,32 +9823,35 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4900</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
@@ -9630,35 +9859,35 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="R94" s="3">
-        <v>100</v>
-      </c>
       <c r="S94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -9684,37 +9913,40 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>600</v>
       </c>
-      <c r="AL94" s="3">
-        <v>0</v>
-      </c>
       <c r="AM94" s="3">
         <v>0</v>
       </c>
       <c r="AN94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,8 +10026,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,80 +10461,83 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-3600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1600</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>3600</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -10300,10 +10545,10 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -10315,28 +10560,31 @@
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4900</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
-      </c>
       <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
         <v>2900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,8 +10621,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10451,120 +10699,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1800</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>3400</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>1400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RAVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>RAVE</t>
   </si>
@@ -656,292 +656,299 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E7" s="2">
         <v>46019</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45928</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45837</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45746</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45655</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45564</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45375</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45284</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45193</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45102</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45011</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44920</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44829</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44647</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44556</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44374</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44283</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44192</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44101</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44010</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43919</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43828</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43737</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43548</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43457</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43366</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43275</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43184</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43093</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43002</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42911</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42820</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42729</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E8" s="3">
         <v>3000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3200</v>
       </c>
       <c r="F8" s="3">
         <v>3200</v>
       </c>
       <c r="G8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3000</v>
       </c>
       <c r="O8" s="3">
         <v>3000</v>
       </c>
       <c r="P8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2900</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>3100</v>
       </c>
       <c r="AE8" s="3">
         <v>3100</v>
       </c>
       <c r="AF8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AG8" s="3">
         <v>3200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -949,10 +956,10 @@
         <v>700</v>
       </c>
       <c r="E9" s="3">
+        <v>700</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>800</v>
       </c>
       <c r="G9" s="3">
         <v>800</v>
@@ -961,10 +968,10 @@
         <v>800</v>
       </c>
       <c r="I9" s="3">
+        <v>800</v>
+      </c>
+      <c r="J9" s="3">
         <v>1000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>800</v>
       </c>
       <c r="K9" s="3">
         <v>800</v>
@@ -973,37 +980,37 @@
         <v>800</v>
       </c>
       <c r="M9" s="3">
+        <v>800</v>
+      </c>
+      <c r="N9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>8</v>
+      <c r="S9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V9" s="3">
-        <v>0</v>
+      <c r="V9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3">
         <v>100</v>
@@ -1024,13 +1031,13 @@
         <v>100</v>
       </c>
       <c r="AD9" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AE9" s="3">
         <v>400</v>
       </c>
       <c r="AF9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AG9" s="3">
         <v>200</v>
@@ -1039,147 +1046,153 @@
         <v>200</v>
       </c>
       <c r="AI9" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1900</v>
       </c>
       <c r="M10" s="3">
         <v>1900</v>
       </c>
       <c r="N10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O10" s="3">
         <v>2100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="3">
         <v>2600</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W10" s="3">
         <v>2400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2800</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>2700</v>
       </c>
       <c r="AE10" s="3">
         <v>2700</v>
       </c>
       <c r="AF10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AG10" s="3">
         <v>3000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1494,14 +1514,14 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1519,11 +1539,11 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-700</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1534,52 +1554,55 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>200</v>
       </c>
-      <c r="AC14" s="3">
-        <v>100</v>
-      </c>
       <c r="AD14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="3">
         <v>1300</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>200</v>
       </c>
       <c r="AF14" s="3">
         <v>200</v>
       </c>
       <c r="AG14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AH14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3">
         <v>100</v>
       </c>
       <c r="AJ14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK14" s="3">
         <v>500</v>
       </c>
-      <c r="AK14" s="3">
-        <v>100</v>
-      </c>
       <c r="AL14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM14" s="3">
         <v>800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>5100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1596,16 +1619,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1626,7 +1649,7 @@
         <v>100</v>
       </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1662,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="3">
         <v>100</v>
@@ -1680,7 +1703,7 @@
         <v>100</v>
       </c>
       <c r="AJ15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AK15" s="3">
         <v>300</v>
@@ -1689,16 +1712,19 @@
         <v>300</v>
       </c>
       <c r="AM15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN15" s="3">
         <v>600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,8 +1763,9 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1746,237 +1773,243 @@
         <v>2300</v>
       </c>
       <c r="E17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2200</v>
       </c>
       <c r="K17" s="3">
         <v>2200</v>
       </c>
       <c r="L17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>2800</v>
       </c>
       <c r="AG17" s="3">
         <v>2800</v>
       </c>
       <c r="AH17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AI17" s="3">
         <v>2900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>14300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>500</v>
       </c>
       <c r="M18" s="3">
         <v>500</v>
       </c>
       <c r="N18" s="3">
+        <v>500</v>
+      </c>
+      <c r="O18" s="3">
         <v>800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>500</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>400</v>
       </c>
       <c r="R18" s="3">
         <v>400</v>
       </c>
       <c r="S18" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T18" s="3">
         <v>500</v>
       </c>
       <c r="U18" s="3">
+        <v>500</v>
+      </c>
+      <c r="V18" s="3">
         <v>300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3">
-        <v>100</v>
-      </c>
       <c r="Y18" s="3">
         <v>100</v>
       </c>
       <c r="Z18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>-400</v>
       </c>
       <c r="AJ18" s="3">
         <v>-400</v>
       </c>
       <c r="AK18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AL18" s="3">
         <v>-200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-7500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,19 +2051,20 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
@@ -2038,11 +2072,11 @@
       <c r="H20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
@@ -2059,18 +2093,18 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -2137,46 +2171,49 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E21" s="3">
         <v>800</v>
       </c>
       <c r="F21" s="3">
+        <v>800</v>
+      </c>
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>700</v>
       </c>
       <c r="I21" s="3">
         <v>700</v>
       </c>
       <c r="J21" s="3">
+        <v>700</v>
+      </c>
+      <c r="K21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>600</v>
       </c>
       <c r="M21" s="3">
         <v>600</v>
       </c>
       <c r="N21" s="3">
+        <v>600</v>
+      </c>
+      <c r="O21" s="3">
         <v>900</v>
-      </c>
-      <c r="O21" s="3">
-        <v>500</v>
       </c>
       <c r="P21" s="3">
         <v>500</v>
@@ -2185,26 +2222,26 @@
         <v>500</v>
       </c>
       <c r="R21" s="3">
+        <v>500</v>
+      </c>
+      <c r="S21" s="3">
         <v>1200</v>
-      </c>
-      <c r="S21" s="3">
-        <v>500</v>
       </c>
       <c r="T21" s="3">
         <v>500</v>
       </c>
       <c r="U21" s="3">
+        <v>500</v>
+      </c>
+      <c r="V21" s="3">
         <v>300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>500</v>
       </c>
-      <c r="X21" s="3">
-        <v>100</v>
-      </c>
       <c r="Y21" s="3">
         <v>100</v>
       </c>
@@ -2212,52 +2249,55 @@
         <v>100</v>
       </c>
       <c r="AA21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
-        <v>100</v>
-      </c>
       <c r="AC21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD21" s="3">
         <v>400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>300</v>
       </c>
-      <c r="AH21" s="3">
-        <v>100</v>
-      </c>
       <c r="AI21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2291,14 +2331,14 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2375,166 +2415,172 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>500</v>
       </c>
       <c r="M23" s="3">
         <v>500</v>
       </c>
       <c r="N23" s="3">
+        <v>500</v>
+      </c>
+      <c r="O23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
-      </c>
-      <c r="S23" s="3">
-        <v>500</v>
       </c>
       <c r="T23" s="3">
         <v>500</v>
       </c>
       <c r="U23" s="3">
+        <v>500</v>
+      </c>
+      <c r="V23" s="3">
         <v>300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
-        <v>100</v>
-      </c>
       <c r="Y23" s="3">
         <v>100</v>
       </c>
       <c r="Z23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
       <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
         <v>300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
       <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>200</v>
       </c>
       <c r="F24" s="3">
+        <v>200</v>
+      </c>
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>100</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
-        <v>100</v>
-      </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
@@ -2542,11 +2588,11 @@
         <v>100</v>
       </c>
       <c r="R24" s="3">
+        <v>100</v>
+      </c>
+      <c r="S24" s="3">
         <v>-5700</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -2569,32 +2615,32 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="3">
         <v>100</v>
       </c>
       <c r="AH24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
@@ -2613,8 +2659,11 @@
       <c r="AO24" s="3">
         <v>0</v>
       </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,46 +2781,49 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E26" s="3">
         <v>600</v>
       </c>
       <c r="F26" s="3">
+        <v>600</v>
+      </c>
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
-      </c>
-      <c r="O26" s="3">
-        <v>300</v>
       </c>
       <c r="P26" s="3">
         <v>300</v>
@@ -2780,117 +2832,120 @@
         <v>300</v>
       </c>
       <c r="R26" s="3">
+        <v>300</v>
+      </c>
+      <c r="S26" s="3">
         <v>6800</v>
-      </c>
-      <c r="S26" s="3">
-        <v>500</v>
       </c>
       <c r="T26" s="3">
         <v>500</v>
       </c>
       <c r="U26" s="3">
+        <v>500</v>
+      </c>
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
-        <v>100</v>
-      </c>
       <c r="Y26" s="3">
         <v>100</v>
       </c>
       <c r="Z26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
       <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3">
         <v>200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
-      <c r="AG26" s="3">
-        <v>100</v>
-      </c>
       <c r="AH26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI26" s="3">
         <v>3300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E27" s="3">
         <v>600</v>
       </c>
       <c r="F27" s="3">
+        <v>600</v>
+      </c>
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>300</v>
       </c>
       <c r="P27" s="3">
         <v>300</v>
@@ -2899,79 +2954,82 @@
         <v>300</v>
       </c>
       <c r="R27" s="3">
+        <v>300</v>
+      </c>
+      <c r="S27" s="3">
         <v>6800</v>
-      </c>
-      <c r="S27" s="3">
-        <v>500</v>
       </c>
       <c r="T27" s="3">
         <v>500</v>
       </c>
       <c r="U27" s="3">
+        <v>500</v>
+      </c>
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
-        <v>100</v>
-      </c>
       <c r="Y27" s="3">
         <v>100</v>
       </c>
       <c r="Z27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
       <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
         <v>200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
       </c>
-      <c r="AG27" s="3">
-        <v>100</v>
-      </c>
       <c r="AH27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI27" s="3">
         <v>3300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3166,14 +3227,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -3185,31 +3246,34 @@
         <v>0</v>
       </c>
       <c r="AH29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3">
         <v>-200</v>
       </c>
       <c r="AL29" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AM29" s="3">
         <v>-300</v>
       </c>
       <c r="AN29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AO29" s="3">
         <v>-400</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,19 +3513,22 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
@@ -3466,11 +3536,11 @@
       <c r="H32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
@@ -3487,18 +3557,18 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3565,46 +3635,49 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E33" s="3">
         <v>600</v>
       </c>
       <c r="F33" s="3">
+        <v>600</v>
+      </c>
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>300</v>
       </c>
       <c r="P33" s="3">
         <v>300</v>
@@ -3613,79 +3686,82 @@
         <v>300</v>
       </c>
       <c r="R33" s="3">
+        <v>300</v>
+      </c>
+      <c r="S33" s="3">
         <v>6800</v>
-      </c>
-      <c r="S33" s="3">
-        <v>500</v>
       </c>
       <c r="T33" s="3">
         <v>500</v>
       </c>
       <c r="U33" s="3">
+        <v>500</v>
+      </c>
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
-        <v>100</v>
-      </c>
       <c r="Y33" s="3">
         <v>100</v>
       </c>
       <c r="Z33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
       <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
         <v>200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200</v>
       </c>
-      <c r="AG33" s="3">
-        <v>100</v>
-      </c>
       <c r="AH33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI33" s="3">
         <v>3300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-7900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,46 +3879,49 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E35" s="3">
         <v>600</v>
       </c>
       <c r="F35" s="3">
+        <v>600</v>
+      </c>
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>300</v>
       </c>
       <c r="P35" s="3">
         <v>300</v>
@@ -3851,203 +3930,209 @@
         <v>300</v>
       </c>
       <c r="R35" s="3">
+        <v>300</v>
+      </c>
+      <c r="S35" s="3">
         <v>6800</v>
-      </c>
-      <c r="S35" s="3">
-        <v>500</v>
       </c>
       <c r="T35" s="3">
         <v>500</v>
       </c>
       <c r="U35" s="3">
+        <v>500</v>
+      </c>
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
-        <v>100</v>
-      </c>
       <c r="Y35" s="3">
         <v>100</v>
       </c>
       <c r="Z35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
       <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
         <v>200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200</v>
       </c>
-      <c r="AG35" s="3">
-        <v>100</v>
-      </c>
       <c r="AH35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI35" s="3">
         <v>3300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-7900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E38" s="2">
         <v>46019</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45928</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45837</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45746</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45655</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45564</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45375</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45284</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45193</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45102</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45011</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44920</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44829</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44647</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44556</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44374</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44283</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44192</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44101</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44010</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43919</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43828</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43737</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43548</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43457</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43366</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43275</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43184</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43093</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43002</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42911</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42820</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42729</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,154 +4218,158 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2300</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>1900</v>
       </c>
       <c r="AF41" s="3">
         <v>1900</v>
       </c>
       <c r="AG41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AH41" s="3">
         <v>2000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E42" s="3">
         <v>10300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4900</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -4370,127 +4460,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2200</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>2300</v>
       </c>
       <c r="AG43" s="3">
         <v>2300</v>
       </c>
       <c r="AH43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AI43" s="3">
         <v>2500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4594,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL44" s="3">
         <v>100</v>
@@ -4603,13 +4699,16 @@
         <v>100</v>
       </c>
       <c r="AN44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AO44" s="3">
         <v>200</v>
       </c>
+      <c r="AP44" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4623,13 +4722,13 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
@@ -4665,7 +4764,7 @@
         <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
@@ -4674,180 +4773,186 @@
         <v>200</v>
       </c>
       <c r="X45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="Y45" s="3">
         <v>500</v>
       </c>
       <c r="Z45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA45" s="3">
         <v>400</v>
       </c>
       <c r="AB45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC45" s="3">
         <v>500</v>
       </c>
       <c r="AD45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE45" s="3">
         <v>600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>900</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>800</v>
       </c>
       <c r="AH45" s="3">
         <v>800</v>
       </c>
       <c r="AI45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E46" s="3">
         <v>13000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8700</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>4900</v>
       </c>
       <c r="Z46" s="3">
         <v>4900</v>
       </c>
       <c r="AA46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AB46" s="3">
         <v>4000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>8300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4887,8 +4992,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>400</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>400</v>
@@ -4897,7 +5002,7 @@
         <v>400</v>
       </c>
       <c r="S47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T47" s="3">
         <v>500</v>
@@ -4906,7 +5011,7 @@
         <v>500</v>
       </c>
       <c r="V47" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="W47" s="3">
         <v>300</v>
@@ -4915,58 +5020,61 @@
         <v>300</v>
       </c>
       <c r="Y47" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="Z47" s="3">
         <v>700</v>
       </c>
       <c r="AA47" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB47" s="3">
         <v>400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>1200</v>
       </c>
       <c r="AF47" s="3">
         <v>1200</v>
       </c>
       <c r="AG47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH47" s="3">
         <v>1000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>300</v>
       </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
-      </c>
       <c r="AK47" s="3">
         <v>0</v>
       </c>
       <c r="AL47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AM47" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN47" s="3">
         <v>200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4974,118 +5082,121 @@
         <v>400</v>
       </c>
       <c r="E48" s="3">
+        <v>400</v>
+      </c>
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>5800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5093,7 +5204,7 @@
         <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
         <v>200</v>
@@ -5108,7 +5219,7 @@
         <v>200</v>
       </c>
       <c r="J49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K49" s="3">
         <v>300</v>
@@ -5132,7 +5243,7 @@
         <v>300</v>
       </c>
       <c r="R49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S49" s="3">
         <v>200</v>
@@ -5147,7 +5258,7 @@
         <v>200</v>
       </c>
       <c r="W49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X49" s="3">
         <v>100</v>
@@ -5156,7 +5267,7 @@
         <v>100</v>
       </c>
       <c r="Z49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA49" s="3">
         <v>200</v>
@@ -5191,8 +5302,8 @@
       <c r="AK49" s="3">
         <v>200</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>8</v>
+      <c r="AL49" s="3">
+        <v>200</v>
       </c>
       <c r="AM49" s="3" t="s">
         <v>8</v>
@@ -5203,8 +5314,11 @@
       <c r="AO49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,8 +5558,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5482,17 +5602,17 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
         <v>5600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>5800</v>
       </c>
       <c r="R52" s="3">
         <v>5800</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
+      <c r="S52" s="3">
+        <v>5800</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
@@ -5500,8 +5620,8 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -5516,31 +5636,31 @@
         <v>0</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>200</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>4200</v>
       </c>
       <c r="AC52" s="3">
         <v>4200</v>
       </c>
       <c r="AD52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AE52" s="3">
         <v>4300</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>3600</v>
       </c>
       <c r="AF52" s="3">
         <v>3600</v>
       </c>
       <c r="AG52" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AH52" s="3">
         <v>3700</v>
       </c>
       <c r="AI52" s="3">
-        <v>200</v>
+        <v>3700</v>
       </c>
       <c r="AJ52" s="3">
         <v>200</v>
@@ -5549,19 +5669,22 @@
         <v>200</v>
       </c>
       <c r="AL52" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AM52" s="3">
         <v>500</v>
       </c>
       <c r="AN52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AO52" s="3">
         <v>200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E54" s="3">
         <v>17500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11100</v>
-      </c>
-      <c r="AF54" s="3">
-        <v>11500</v>
       </c>
       <c r="AG54" s="3">
         <v>11500</v>
       </c>
       <c r="AH54" s="3">
+        <v>11500</v>
+      </c>
+      <c r="AI54" s="3">
         <v>11000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>8200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>12000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>11000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,97 +6014,98 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>400</v>
       </c>
       <c r="J57" s="3">
         <v>400</v>
       </c>
       <c r="K57" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>700</v>
       </c>
       <c r="M57" s="3">
+        <v>700</v>
+      </c>
+      <c r="N57" s="3">
         <v>600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>500</v>
       </c>
       <c r="O57" s="3">
         <v>500</v>
       </c>
       <c r="P57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>700</v>
       </c>
       <c r="R57" s="3">
         <v>700</v>
       </c>
       <c r="S57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="T57" s="3">
         <v>600</v>
       </c>
       <c r="U57" s="3">
+        <v>600</v>
+      </c>
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>900</v>
       </c>
       <c r="Z57" s="3">
         <v>900</v>
       </c>
       <c r="AA57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB57" s="3">
         <v>700</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>900</v>
       </c>
       <c r="AC57" s="3">
         <v>900</v>
       </c>
       <c r="AD57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE57" s="3">
         <v>1200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>800</v>
       </c>
       <c r="AG57" s="3">
         <v>800</v>
@@ -5983,33 +6114,36 @@
         <v>800</v>
       </c>
       <c r="AI57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
@@ -6039,13 +6173,13 @@
         <v>400</v>
       </c>
       <c r="N58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O58" s="3">
         <v>500</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -6054,20 +6188,20 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>1700</v>
       </c>
       <c r="V58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W58" s="3">
         <v>1800</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
@@ -6080,8 +6214,8 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -6108,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL58" s="3">
         <v>1000</v>
@@ -6119,37 +6253,40 @@
       <c r="AN58" s="3">
         <v>1000</v>
       </c>
-      <c r="AO58" s="3" t="s">
+      <c r="AO58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AP58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
       </c>
       <c r="F59" s="3">
+        <v>100</v>
+      </c>
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
       <c r="I59" s="3">
+        <v>100</v>
+      </c>
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
@@ -6158,210 +6295,216 @@
         <v>200</v>
       </c>
       <c r="N59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1700</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1600</v>
       </c>
       <c r="Y59" s="3">
         <v>1600</v>
       </c>
       <c r="Z59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AI59" s="3">
-        <v>1000</v>
       </c>
       <c r="AJ59" s="3">
         <v>1000</v>
       </c>
       <c r="AK59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AL59" s="3">
         <v>1400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1900</v>
-      </c>
-      <c r="AN59" s="3">
-        <v>1400</v>
       </c>
       <c r="AO59" s="3">
         <v>1400</v>
       </c>
+      <c r="AP59" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2000</v>
       </c>
       <c r="J60" s="3">
         <v>2000</v>
       </c>
       <c r="K60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2300</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>2500</v>
       </c>
       <c r="Z60" s="3">
         <v>2500</v>
       </c>
       <c r="AA60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AB60" s="3">
         <v>2600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6369,41 +6512,41 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>100</v>
+      </c>
+      <c r="G61" s="3">
         <v>200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>500</v>
-      </c>
-      <c r="J61" s="3">
-        <v>600</v>
       </c>
       <c r="K61" s="3">
         <v>600</v>
       </c>
       <c r="L61" s="3">
+        <v>600</v>
+      </c>
+      <c r="M61" s="3">
         <v>700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6423,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>2200</v>
@@ -6435,7 +6578,7 @@
         <v>2200</v>
       </c>
       <c r="AA61" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="AB61" s="3">
         <v>1500</v>
@@ -6444,7 +6587,7 @@
         <v>1500</v>
       </c>
       <c r="AD61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="AE61" s="3">
         <v>1600</v>
@@ -6462,25 +6605,28 @@
         <v>1600</v>
       </c>
       <c r="AJ61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AK61" s="3">
         <v>1500</v>
-      </c>
-      <c r="AK61" s="3">
-        <v>2700</v>
       </c>
       <c r="AL61" s="3">
         <v>2700</v>
       </c>
       <c r="AM61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AN61" s="3">
         <v>2800</v>
       </c>
-      <c r="AN61" s="3">
-        <v>0</v>
-      </c>
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6520,86 +6666,89 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>1900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,43 +7110,46 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2400</v>
       </c>
       <c r="G66" s="3">
         <v>2400</v>
       </c>
       <c r="H66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I66" s="3">
         <v>2300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3900</v>
-      </c>
-      <c r="N66" s="3">
-        <v>3800</v>
       </c>
       <c r="O66" s="3">
         <v>3800</v>
@@ -7000,82 +7158,85 @@
         <v>3800</v>
       </c>
       <c r="Q66" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="R66" s="3">
         <v>5100</v>
       </c>
       <c r="S66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T66" s="3">
         <v>4700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>11600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>10200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E72" s="3">
         <v>8900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="Z72" s="3">
-        <v>-8700</v>
       </c>
       <c r="AA72" s="3">
         <v>-8700</v>
       </c>
       <c r="AB72" s="3">
-        <v>-4200</v>
+        <v>-8700</v>
       </c>
       <c r="AC72" s="3">
         <v>-4200</v>
       </c>
       <c r="AD72" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-4800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-1300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E76" s="3">
         <v>15500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>500</v>
       </c>
-      <c r="AA76" s="3">
-        <v>100</v>
-      </c>
       <c r="AB76" s="3">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="AC76" s="3">
         <v>4700</v>
       </c>
       <c r="AD76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AE76" s="3">
         <v>4400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-2100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>-900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,170 +8496,176 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E80" s="2">
         <v>46019</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45928</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45837</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45746</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45655</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45564</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45375</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45284</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45193</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45102</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45011</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44920</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44829</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44647</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44556</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44374</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44283</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44192</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44101</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44010</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43919</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43828</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43737</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43548</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43457</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43366</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43275</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43184</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43093</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43002</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42911</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42820</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42729</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E81" s="3">
         <v>600</v>
       </c>
       <c r="F81" s="3">
+        <v>600</v>
+      </c>
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>300</v>
       </c>
       <c r="P81" s="3">
         <v>300</v>
@@ -8479,79 +8674,82 @@
         <v>300</v>
       </c>
       <c r="R81" s="3">
+        <v>300</v>
+      </c>
+      <c r="S81" s="3">
         <v>6800</v>
-      </c>
-      <c r="S81" s="3">
-        <v>500</v>
       </c>
       <c r="T81" s="3">
         <v>500</v>
       </c>
       <c r="U81" s="3">
+        <v>500</v>
+      </c>
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
-        <v>100</v>
-      </c>
       <c r="Y81" s="3">
         <v>100</v>
       </c>
       <c r="Z81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
       <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
         <v>200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200</v>
       </c>
-      <c r="AG81" s="3">
-        <v>100</v>
-      </c>
       <c r="AH81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI81" s="3">
         <v>3300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-7900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,8 +8791,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8641,7 +8840,7 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -8677,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="AD83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE83" s="3">
         <v>100</v>
@@ -8695,7 +8894,7 @@
         <v>100</v>
       </c>
       <c r="AJ83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AK83" s="3">
         <v>300</v>
@@ -8704,16 +8903,19 @@
         <v>300</v>
       </c>
       <c r="AM83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN83" s="3">
         <v>600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>400</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-500</v>
       </c>
       <c r="AB89" s="3">
         <v>-500</v>
       </c>
       <c r="AC89" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="AD89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
       <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,8 +9689,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9489,11 +9710,11 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -9511,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -9520,7 +9741,7 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -9529,11 +9750,11 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -9565,31 +9786,34 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AL91" s="3">
-        <v>-300</v>
       </c>
       <c r="AM91" s="3">
         <v>-300</v>
       </c>
       <c r="AN91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,35 +10053,38 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4900</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -9862,35 +10092,35 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
-        <v>100</v>
-      </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -9916,37 +10146,40 @@
         <v>0</v>
       </c>
       <c r="AF94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>600</v>
       </c>
-      <c r="AM94" s="3">
-        <v>0</v>
-      </c>
       <c r="AN94" s="3">
         <v>0</v>
       </c>
       <c r="AO94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10029,8 +10263,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,8 +10707,11 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10475,72 +10721,72 @@
       <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1600</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>3600</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -10548,10 +10794,10 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
@@ -10563,28 +10809,31 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>4900</v>
       </c>
-      <c r="AL100" s="3">
-        <v>0</v>
-      </c>
       <c r="AM100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3">
         <v>2900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10624,8 +10873,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10702,123 +10951,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1800</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>3400</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>1400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-800</v>
       </c>
     </row>
